--- a/KAMCHATKA_OPEN_ZAPROS_2710.xlsx
+++ b/KAMCHATKA_OPEN_ZAPROS_2710.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приводы и прочее" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Кому запросить'!$A$1:$M$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Кому запросить'!$A$1:$M$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Краны'!$A$1:$V$125</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Затворы'!$A$1:$V$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Клапаны'!$A$1:$V$14</definedName>
@@ -50,7 +50,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -99,7 +104,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -132,6 +137,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -601,10 +609,10 @@
         <v>16</v>
       </c>
       <c r="D5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>3</v>
@@ -623,13 +631,13 @@
         <v>33</v>
       </c>
       <c r="D6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="7" ht="48" customHeight="1">
@@ -645,13 +653,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8" ht="48" customHeight="1">
@@ -667,10 +675,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0</v>
@@ -689,13 +697,13 @@
         <v>2413</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1">
@@ -858,7 +866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1327,60 +1335,60 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>ООО «ПромАрм» (PromArm®)</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>Компания «Арматон»</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>завод</t>
+          <t>дистрибьютор</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>г. Пенза, ул. Баумана, 101В (производство); офис Москва, Пресненская наб., 12</t>
+          <t>Москва (Новая Москва)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97</t>
+          <t>+7 (963) 728-59-82</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>info@promarm.ru</t>
+          <t>armaton@bk.ru</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>https://www.promarm.com (promarm.ru — из среды не открылся)</t>
+          <t>http://armaton.ru</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1.1/23, 1.1/22, 1.3/150</t>
+          <t>1.3/40, 1.3/45, 1.3/46, 1.3/47, 1.3/56, 1.3/57</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Держатель марки ПА954: в каталоге есть ровно «ПА954.450.10-05» — трёхэксцентриковый межфланцевый с гладкими проушинами, корпус и диск нерж. сталь с молибденом (CF8M), седло PTFE, DN450 PN10 (1.1/23 — </t>
+          <t>Узкий профиль: сильфонная и вакуумная арматура с 2002 г. В номенклатуре: 22Б16п и 22Б17п (латунные сильфонные хладоновые, редкая позиция 1.3/40), 14нж17ст / 14нж19п (сильфонные нерж., как вариант 14нж</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>не найдено (в разделе «Документы, сертификаты» — ТР ТС 032, сертификат РМРС, гиг</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>https://www.promarm.com/contacts/</t>
+          <t>http://armaton.ru/kontakty ; http://armaton.ru/</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1398,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1405,45 +1413,45 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>г. Пенза (промкомплекс 225 000 м²)</t>
+          <t>Старый Оскол (Белгородская обл.); офис продаж — Москва</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 (продажи)</t>
+          <t>+7 (4725) 469-470 (завод)</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>sales@ptpa.ru</t>
+          <t>zavod@saz-avangard.ru</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://ptpa.ru</t>
+          <t>https://saz-avangard.ru</t>
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>1.3/150, 1.1/23, 1.1/22</t>
+          <t>1.3/2, 1.3/3, 1.3/4, 1.3/5, 1.3/163</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Затворы дисковые поворотные стальные DN400–2000 PN0,25–1,6 МПа (ПТ99052-500ТУ, ГОСТ 13547-2015) и трёхэксцентриковые DN50–2000 PN1,6–4,0 МПа (ТУ3742-038-05749375-2007), нерж. исполнение до +550 °C — а</t>
+          <t>Собственное производство 25ч945п: чугунный фланцевый односедельный клапан, Ду15–300, Ру16, t −15…+150 °C, ТУ 3722-…, комплектуется российским ЭИМ ПЭП-САЗ (стандарт/IN/Ex). Ду15/25/50/80 есть в каталог</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>не найдено на сайте</t>
+          <t>ДА: Заключение Минпромторга о подтверждении производства в РФ (ПП 719), заявлени</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://ptpa.ru/contacts/</t>
+          <t>https://saz-avangard.ru/contacts/ ; https://saz-avangard.ru/catalog/klapany-reg/odnosedelniy-chugunniy-eim/25ch945p/ ; https://saz-avangard.ru/upload/iblock/8f1/i8qtd4llupat9fpta48v2vwrbz2fj2sn/Zaklyu</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1461,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -1468,45 +1476,45 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Челябинская обл., г. Озёрск, ул. Индустриальная, 4</t>
+          <t>Пермь</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 307-71-09</t>
+          <t>+7 (342) 270-07-34</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>info@aoutk.ru</t>
+          <t>sales@ptza.ru</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://aoutk.ru</t>
+          <t>https://www.ptza.ru</t>
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.1/22, 1.1/23</t>
+          <t>1.3/56, 1.3/57, 1.3/23, 1.3/24</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>MV UBZ1 межфланцевый с эластомерным седлом: DN25–600, PN6/10/16/25, корпус GGG40 / WCB / CF8 / CF8M, верхний фланец ISO 5211, класс А — закрывает чугунные межфланцевые Ду65–200 Ру16 и как аналог Stens</t>
+          <t>15нж65нж: фланцевый, Ду10–200 (есть Ду125 и Ду150), Ру1,6 МПа, корпус 12Х18Н9ТЛ / 08Х18Н10Т. 16нж10нж: подъёмный обратный, Ду10–200 (Ду32 — L180 мм, Ду50 — L230 мм), Ру1,6 МПа, корпус 08Х18Н10/12Х18Н9</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>не найдено (на странице сертификатов — только декларации ЕАЭС ТР ТС 010/032)</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://aoutk.ru/contacts</t>
+          <t>https://www.ptza.ru/kontakty/ ; https://www.ptza.ru/15nzh65nzh-klapan-zapornyj/ ; https://www.ptza.ru/16nzh10nzh-klapan-obratnyj-podemnyj/</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1524,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>АО «АБС ЗЭиМ Автоматизация»</t>
+          <t>ООО «ПромАрм» (PromArm®)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1531,45 +1539,45 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>г. Чебоксары, пр-т И. Яковлева, 1</t>
+          <t>г. Пенза, ул. Баумана, 101В (производство); офис Москва, Пресненская наб., 12</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>+7 (8352) 30-51-48</t>
+          <t>+7 (8412) 35-07-97</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>sales@zeim.ru</t>
+          <t>info@promarm.ru</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.zeim.ru</t>
+          <t>https://www.promarm.com (promarm.ru — из среды не открылся)</t>
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>1.3/163, 1.6/93</t>
+          <t>1.1/23, 1.1/22, 1.3/150</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Аналог Regada ST0 490.0 (1.3/163): прямоходные МЭПК-800/1600/2500-99 (усилие 800/1600/2500 Н, ход 20/40 мм, 220/230/240 В, IP54/65, У1…УХЛ1) — подобрать по усилию/ходу клапана. Аналог ESBE 95 (1.6/93,</t>
+          <t xml:space="preserve">Держатель марки ПА954: в каталоге есть ровно «ПА954.450.10-05» — трёхэксцентриковый межфланцевый с гладкими проушинами, корпус и диск нерж. сталь с молибденом (CF8M), седло PTFE, DN450 PN10 (1.1/23 — </t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>не найдено на сайте</t>
+          <t>не найдено (в разделе «Документы, сертификаты» — ТР ТС 032, сертификат РМРС, гиг</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.zeim.ru/contacts/</t>
+          <t>https://www.promarm.com/contacts/</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1587,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
+          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1594,45 +1602,45 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Рыбинск (Ярославская обл.)</t>
+          <t>г. Пенза (промкомплекс 225 000 м²)</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>8-800-700-62-60</t>
+          <t>8 800 444-00-28 (продажи)</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>info@fobosarm.ru</t>
+          <t>sales@ptpa.ru</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>fobosarm.ru</t>
+          <t>https://ptpa.ru</t>
         </is>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.3/135</t>
+          <t>1.3/150, 1.1/23, 1.1/22</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Кран шаровый муфтовый Ду6–50, Ру до 6,3 МПа; корпус 1.4408 (литьё, аналог CF8M/AISI 316 ≈ 08Х17Н13М2) или 12Х18Н9ТЛ/12Х18Н10Т; седло фторопласт Ф4; серии МОНО/ЭКОНОМ/РЕТРО. ВНИМАНИЕ: на сайте температ</t>
+          <t>Затворы дисковые поворотные стальные DN400–2000 PN0,25–1,6 МПа (ПТ99052-500ТУ, ГОСТ 13547-2015) и трёхэксцентриковые DN50–2000 PN1,6–4,0 МПа (ТУ3742-038-05749375-2007), нерж. исполнение до +550 °C — а</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>не найдено (запросить у завода)</t>
+          <t>не найдено на сайте</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://fobosarm.ru/contacts/</t>
+          <t>https://ptpa.ru/contacts/</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1650,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ООО «НПП «Промышленная автоматика» (НПП «ПРОМА»)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Челябинский завод трубопроводной арматуры» (ООО «ЧЗТА», бренд «ЧЗТА АРМАКОМ»)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1657,35 +1665,35 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>г. Казань, ул. Г. Тукая, 125к6 (фактический адрес)</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>8 (843) 558-25-28</t>
+          <t>+7 (351) 215-53-33</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>info@promav.ru</t>
+          <t>zakaz@chzta.ru</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://www.promav.ru</t>
+          <t>https://chzta.ru</t>
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1.3/163</t>
+          <t>1.1/6, 1.3/23, 1.3/24</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>МЭП-М (механизм электрический исполнительный прямоходный, ТУ 4218-033-04880601-2004), исполнения 800/30-220, 1600/45-400, 5000/60-530 — аналог Regada ST0. Страница о производстве без описания цехов; д</t>
+          <t>1.1/6: в каталоге есть именно «Задвижка нержавеющая 30нж947нж Ду1000 Ру4», сталь 12Х18Н10Т, фланцевая, под электропривод, масса 1085 кг, класс А, под заказ, «по ГОСТ и чертежам Заказчика». Присоединен</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1695,7 +1703,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://www.promav.ru/contacts/</t>
+          <t>https://chzta.ru/contacts/ ; https://chzta.ru/catalog/30nzh947nzh/zadvizhka-nerzhaveyushchaya-du-1000-ru-4-30nzh947nzh/ ; https://chzta.ru/upload/download/company_details.pdf</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1713,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ООО «ПКФ «ТЕРМ»</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Нижегородский завод «Старт»</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1720,35 +1728,35 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>г. Саратов, ул. Танкистов, 195</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+7 (927) 279-09-83</t>
+          <t>+7 (831) 253-83-11</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>term1998@yandex.ru</t>
+          <t>start.nn@mail.ru</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://pkfterm.ru</t>
+          <t>https://start-nn.ru</t>
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1.4/1</t>
+          <t>1.3/45, 1.3/46, 1.3/47</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>«Специализируется на производстве рыбозащитных оголовков с потокообразователем (РОП) моделей СРО и СРБ»; тип РЗУ — «жалюзийный экран с потокообразователем» по СП 101.13330.2023; СРО-20…350 (до 0,35 м³</t>
+          <t>Собственный выпуск сильфонных клапанов 14нж17п / 14нж17ст / 14с17п. Штуцерно-торцевые исполнения: 14нж17п28, 14нж017п31, 14нж917п34 (по сути цапковые), Ду10–150 Ру10. 14нж17п Ду15/25/32 Ру10 нерж. с у</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1758,7 +1766,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://pkfterm.ru/ (блок «Контактная информация»; сайт одностраничный)</t>
+          <t>https://start-nn.ru/contacts/ ; https://start-nn.ru/production/bellows/</t>
         </is>
       </c>
     </row>
@@ -1768,65 +1776,821 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
+          <t>АО «Пензенский арматурный завод» (АО «ПАЗ»)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Пенза</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+7 (8412) 20-11-00</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>info@armpaz.ru</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>https://armatura-paz.ru</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>1.3/150, 1.1/22, 1.1/23</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Дисковые затворы производства АО «ПАЗ», в том числе трёхэксцентриковые: DN50–2000, межфланцевые, фланцевые, под приварку; корпус и диск могут быть нержавеющими; привод — редуктор, электро- или пневмоп</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>не найдено (на сайте не указано)</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>https://armatura-paz.ru/contacts ; https://armatura-paz.ru/catalog/obshchepromyshlennaya-armatura/diskovye-zatvory</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="48" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Челябинская обл., г. Озёрск, ул. Индустриальная, 4</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+7 (351) 307-71-09</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>info@aoutk.ru</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>https://aoutk.ru</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>1.1/22, 1.1/23</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>MV UBZ1 межфланцевый с эластомерным седлом: DN25–600, PN6/10/16/25, корпус GGG40 / WCB / CF8 / CF8M, верхний фланец ISO 5211, класс А — закрывает чугунные межфланцевые Ду65–200 Ру16 и как аналог Stens</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>не найдено (на странице сертификатов — только декларации ЕАЭС ТР ТС 010/032)</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>https://aoutk.ru/contacts</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="48" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>АО «АБС ЗЭиМ Автоматизация»</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>г. Чебоксары, пр-т И. Яковлева, 1</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>+7 (8352) 30-51-48</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>sales@zeim.ru</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.zeim.ru</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>1.3/163, 1.6/93</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Аналог Regada ST0 490.0 (1.3/163): прямоходные МЭПК-800/1600/2500-99 (усилие 800/1600/2500 Н, ход 20/40 мм, 220/230/240 В, IP54/65, У1…УХЛ1) — подобрать по усилию/ходу клапана. Аналог ESBE 95 (1.6/93,</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>не найдено на сайте</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>https://www.zeim.ru/contacts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="48" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>ООО ПО «Нефтехимавтоматика» (НХА)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Москва (офис); производство — г. Киреевск, Тульская обл., ул. Тесакова, 9-Г</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>8-800-350-65-67</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>zakaz@nhavtomatika.ru</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>https://nhavtomatika.ru</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>1.1/22, 1.1/23</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Трёхэксцентриковые затворы НХА-7: DN50–1200, PN10–100. Межфланцевое (МФ), фланцевое и приварное исполнения. Корпус и диск: 08Х18Н10 (CF8) или 10Х17Н13М2Т (CF8M). Уплотнение — шихтованное 12Х18Н10 + гр</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>https://nhavtomatika.ru/contacts/ ; https://nhavtomatika.ru/catalog_self/truboprovodnaya_armatura/zatvory/zatvory_disk_treh_flanc_pnevmoprivod/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="48" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Рыбинск (Ярославская обл.)</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>8-800-700-62-60</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>info@fobosarm.ru</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>fobosarm.ru</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>1.3/135</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Кран шаровый муфтовый Ду6–50, Ру до 6,3 МПа; корпус 1.4408 (литьё, аналог CF8M/AISI 316 ≈ 08Х17Н13М2) или 12Х18Н9ТЛ/12Х18Н10Т; седло фторопласт Ф4; серии МОНО/ЭКОНОМ/РЕТРО. ВНИМАНИЕ: на сайте температ</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>не найдено (запросить у завода)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>https://fobosarm.ru/contacts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ООО «НПП «Промышленная автоматика» (НПП «ПРОМА»)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>г. Казань, ул. Г. Тукая, 125к6 (фактический адрес)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>8 (843) 558-25-28</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>info@promav.ru</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.promav.ru</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>1.3/163</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>МЭП-М (механизм электрический исполнительный прямоходный, ТУ 4218-033-04880601-2004), исполнения 800/30-220, 1600/45-400, 5000/60-530 — аналог Regada ST0. Страница о производстве без описания цехов; д</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>https://www.promav.ru/contacts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ПКФ «ТЕРМ»</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>г. Саратов, ул. Танкистов, 195</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>+7 (927) 279-09-83</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>term1998@yandex.ru</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>https://pkfterm.ru</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>1.4/1</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>«Специализируется на производстве рыбозащитных оголовков с потокообразователем (РОП) моделей СРО и СРБ»; тип РЗУ — «жалюзийный экран с потокообразователем» по СП 101.13330.2023; СРО-20…350 (до 0,35 м³</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>https://pkfterm.ru/ (блок «Контактная информация»; сайт одностраничный)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="48" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
           <t>ООО «Регул»</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>известный</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>завод</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>г. Чебоксары, пр-д Машиностроителей, 1 (территория ОАО «Текстильмаш») — производство; офис Москва</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>+7 (499) 653-65-06</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>regyl21@mail.ru</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>https://regul21.ru</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="I22" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>1.4/1</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="K22" s="4" t="inlineStr">
         <is>
           <t>Рыбозащитный оголовок с потокообразователем РОП (перфорированный конус; расход потокообразователя 7 %, напор 30 м; до 85…1050 м³/ч), изготовление нестандартных размеров по ТЗ/чертежам заказчика.</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>не найдено</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>https://regul21.ru/contacts</t>
         </is>
       </c>
     </row>
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ПЭК — «Поволжская Электротехническая Компания» (сайт piek.ru)</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Чебоксары</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>+7 (8352) 57-05-16</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>info@piek.ru</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>https://piek.ru</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>1.3/163</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Российский аналог Regada ST0 490.0 — прямоходный МЭП-2500: усилие 2500 Н, ходы 10/20/30/60 мм, 220/380 В, IP65/67, блок БКВ с токовым датчиком 4–20 мА. По ТЗ нужен ход 25 мм (ближайший — 30 мм) и скор</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>https://piek.ru/contacts/ ; https://piek.ru/mechanisms-mep/2500/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="48" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ТЕД Газовые системы (TEDGAS; сервисный центр DUNGS; домен dungs.ru ведёт на tedgas.ru)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Москва</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>8-800-550-60-80</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>info@tedgas.ru (отдел продаж: retail@karldungs.ru)</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>https://tedgas.ru</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>1.6/92</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В каталоге есть ровно артикул из ТЗ: DUNGS LGV 507/5 230 VAC IP54, арт. 119271 (по каталогу это нормально открытый, сбросной клапан). Компанию основали бывшие сотрудники представительства Karl Dungs; </t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>нет (импорт DUNGS, Германия)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>https://tedgas.ru/kontakti ; https://tedgas.ru/catalog/elektromagnitnie_klapani-3/lgv_elektromagnitny_klapan_normalno_otkrity-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Фирменный магазин ESBE (esbeshop.ru)</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Москва, ул. Кантемировская, 58</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>8-800-333-12-09</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>info@esbeshop.ru</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>https://esbeshop.ru</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>1.6/93</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Точный артикул ESBE 95, 12051900 (230 В, 15 Н·м, 3-точечный, 30–180°, 60 с/90°), «Есть в наличии». Производство — Швеция (импорт). Российский аналог (Ридан AMB) уже в списке известных.</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>нет (импорт, Швеция)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>https://esbeshop.ru/contacts ; https://esbeshop.ru/elektricheskij-privod-povorotnyj-3-tochechnyj-esbe-95-220v-15nm-30-180-60sek-90-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Аврора» (avrora-arm.ru)</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Москва, ул. Зеленодольская, д. 3</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>+7 (495) 956-62-18</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>sales@avrora-arm.ru</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>https://avrora-arm.ru</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>1.3/163</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В каталоге прямоходные приводы REGADA серии Standard (ST 0, ST 0.1, ST 2, MTR), то есть поставка оригинала ST0 490.0-00TQV/00. Статус официального дистрибьютора на сайте не заявлен. Оригинал — импорт </t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>нет (импорт REGADA, Словакия)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>https://avrora-arm.ru/contact-us/ ; https://avrora-arm.ru/produkcziya/elektroprivodyi/regada/pryamoxodnyie/standard/elektroprivod-pryamoxodnyij-st-2-regada.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ПО БЗТпА» (Брянский завод трубопроводной арматуры, bztpa.ru)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Москва (юр. адрес); склад готовой продукции — Брянск, Московский пр-д, 29</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>+7 (4832) 32-20-22</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>info@bztpa.ru</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>https://bztpa.ru</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>1.3/150</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>В номенклатуре «Затвор 32нж910р» DN150–2200, в том числе DN1000. Из материалов указаны 10Х18Н9Т и 08Х17Н13М2 (для морской воды предпочтительнее 08Х17Н13М2). Электропривод (по ТЗ ГЗ-В 600) и КОФ — отде</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>не найдено</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>https://bztpa.ru/contact ; https://bztpa.ru/zatvory-stalnye</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M15"/>
+  <autoFilter ref="A1:M27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1981,7 +2745,7 @@
       <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>1.1/14</t>
         </is>
@@ -2085,7 +2849,7 @@
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>1.1/15</t>
         </is>
@@ -2189,7 +2953,7 @@
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>1.1/16</t>
         </is>
@@ -2289,7 +3053,7 @@
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1.1/17</t>
         </is>
@@ -2393,7 +3157,7 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>1.1/18</t>
         </is>
@@ -2493,7 +3257,7 @@
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>1.1/19</t>
         </is>
@@ -2597,7 +3361,7 @@
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>1.1/20</t>
         </is>
@@ -2705,7 +3469,7 @@
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>1.1/21</t>
         </is>
@@ -2811,7 +3575,7 @@
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>1.2/1</t>
         </is>
@@ -2919,7 +3683,7 @@
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>1.2/2</t>
         </is>
@@ -3023,7 +3787,7 @@
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>1.2/3</t>
         </is>
@@ -3127,7 +3891,7 @@
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>1.2/4</t>
         </is>
@@ -3231,7 +3995,7 @@
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>1.2/5</t>
         </is>
@@ -3340,7 +4104,7 @@
       <c r="A15" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>1.3/101</t>
         </is>
@@ -3444,7 +4208,7 @@
       <c r="A16" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>1.3/102</t>
         </is>
@@ -3548,7 +4312,7 @@
       <c r="A17" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>1.3/103</t>
         </is>
@@ -3648,7 +4412,7 @@
       <c r="A18" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>1.3/104</t>
         </is>
@@ -3752,7 +4516,7 @@
       <c r="A19" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>1.3/105</t>
         </is>
@@ -3856,7 +4620,7 @@
       <c r="A20" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>1.3/106</t>
         </is>
@@ -3964,7 +4728,7 @@
       <c r="A21" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>1.3/107</t>
         </is>
@@ -4072,7 +4836,7 @@
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>1.3/108</t>
         </is>
@@ -4180,7 +4944,7 @@
       <c r="A23" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>1.3/109</t>
         </is>
@@ -4284,7 +5048,7 @@
       <c r="A24" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>1.3/110</t>
         </is>
@@ -4388,7 +5152,7 @@
       <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>1.3/111</t>
         </is>
@@ -4492,7 +5256,7 @@
       <c r="A26" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr">
         <is>
           <t>1.3/112</t>
         </is>
@@ -4596,7 +5360,7 @@
       <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
         <is>
           <t>1.3/113</t>
         </is>
@@ -4699,7 +5463,7 @@
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>1.3/114</t>
         </is>
@@ -4795,7 +5559,7 @@
       <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>1.3/115</t>
         </is>
@@ -4899,7 +5663,7 @@
       <c r="A30" s="5" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>1.3/116</t>
         </is>
@@ -5002,7 +5766,7 @@
       <c r="A31" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="10" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>1.3/117</t>
         </is>
@@ -5106,7 +5870,7 @@
       <c r="A32" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="10" t="inlineStr">
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>1.3/118</t>
         </is>
@@ -5210,7 +5974,7 @@
       <c r="A33" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B33" s="11" t="inlineStr">
         <is>
           <t>1.3/119</t>
         </is>
@@ -5314,7 +6078,7 @@
       <c r="A34" s="5" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="10" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>1.3/120</t>
         </is>
@@ -5418,7 +6182,7 @@
       <c r="A35" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="10" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
         <is>
           <t>1.3/121</t>
         </is>
@@ -5522,7 +6286,7 @@
       <c r="A36" s="5" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
         <is>
           <t>1.3/122</t>
         </is>
@@ -5626,7 +6390,7 @@
       <c r="A37" s="5" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="10" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>1.3/123</t>
         </is>
@@ -5730,7 +6494,7 @@
       <c r="A38" s="5" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="10" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>1.3/124</t>
         </is>
@@ -5834,7 +6598,7 @@
       <c r="A39" s="5" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="10" t="inlineStr">
+      <c r="B39" s="11" t="inlineStr">
         <is>
           <t>1.3/125</t>
         </is>
@@ -5938,7 +6702,7 @@
       <c r="A40" s="5" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="10" t="inlineStr">
+      <c r="B40" s="11" t="inlineStr">
         <is>
           <t>1.3/126</t>
         </is>
@@ -6042,7 +6806,7 @@
       <c r="A41" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="10" t="inlineStr">
+      <c r="B41" s="11" t="inlineStr">
         <is>
           <t>1.3/127</t>
         </is>
@@ -6151,7 +6915,7 @@
       <c r="A42" s="5" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>1.3/128</t>
         </is>
@@ -6260,7 +7024,7 @@
       <c r="A43" s="5" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="10" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>1.3/129</t>
         </is>
@@ -6369,7 +7133,7 @@
       <c r="A44" s="5" t="n">
         <v>43</v>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>1.3/130</t>
         </is>
@@ -6478,7 +7242,7 @@
       <c r="A45" s="5" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="10" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>1.3/131</t>
         </is>
@@ -6578,7 +7342,7 @@
       <c r="A46" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="10" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>1.3/132</t>
         </is>
@@ -6678,7 +7442,7 @@
       <c r="A47" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>1.3/133</t>
         </is>
@@ -6778,7 +7542,7 @@
       <c r="A48" s="5" t="n">
         <v>47</v>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>1.3/134</t>
         </is>
@@ -6878,7 +7642,7 @@
       <c r="A49" s="5" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>1.3/135</t>
         </is>
@@ -6978,7 +7742,7 @@
       <c r="A50" s="5" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="10" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>1.3/136</t>
         </is>
@@ -7078,7 +7842,7 @@
       <c r="A51" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="B51" s="10" t="inlineStr">
+      <c r="B51" s="11" t="inlineStr">
         <is>
           <t>1.3/137</t>
         </is>
@@ -7182,7 +7946,7 @@
       <c r="A52" s="5" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="10" t="inlineStr">
+      <c r="B52" s="11" t="inlineStr">
         <is>
           <t>1.3/138</t>
         </is>
@@ -7286,7 +8050,7 @@
       <c r="A53" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="10" t="inlineStr">
+      <c r="B53" s="11" t="inlineStr">
         <is>
           <t>1.3/139</t>
         </is>
@@ -7390,7 +8154,7 @@
       <c r="A54" s="5" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="10" t="inlineStr">
+      <c r="B54" s="11" t="inlineStr">
         <is>
           <t>1.3/140</t>
         </is>
@@ -7490,7 +8254,7 @@
       <c r="A55" s="5" t="n">
         <v>54</v>
       </c>
-      <c r="B55" s="10" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>1.3/141</t>
         </is>
@@ -7590,7 +8354,7 @@
       <c r="A56" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>1.3/142</t>
         </is>
@@ -7690,7 +8454,7 @@
       <c r="A57" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="B57" s="10" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>1.3/143</t>
         </is>
@@ -7790,7 +8554,7 @@
       <c r="A58" s="5" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="10" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>1.3/144</t>
         </is>
@@ -7890,7 +8654,7 @@
       <c r="A59" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>1.3/145</t>
         </is>
@@ -7990,7 +8754,7 @@
       <c r="A60" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="10" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>1.3/146</t>
         </is>
@@ -8094,7 +8858,7 @@
       <c r="A61" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="10" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>1.3/147</t>
         </is>
@@ -8198,7 +8962,7 @@
       <c r="A62" s="5" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="10" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>1.3/148</t>
         </is>
@@ -8298,7 +9062,7 @@
       <c r="A63" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="10" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>1.3/149</t>
         </is>
@@ -8394,7 +9158,7 @@
       <c r="A64" s="5" t="n">
         <v>63</v>
       </c>
-      <c r="B64" s="10" t="inlineStr">
+      <c r="B64" s="11" t="inlineStr">
         <is>
           <t>1.5/4</t>
         </is>
@@ -8498,7 +9262,7 @@
       <c r="A65" s="5" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="10" t="inlineStr">
+      <c r="B65" s="11" t="inlineStr">
         <is>
           <t>1.5/5</t>
         </is>
@@ -8606,7 +9370,7 @@
       <c r="A66" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="B66" s="10" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>1.5/6</t>
         </is>
@@ -8706,7 +9470,7 @@
       <c r="A67" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="10" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>1.5/7</t>
         </is>
@@ -8810,7 +9574,7 @@
       <c r="A68" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>1.5/8</t>
         </is>
@@ -8914,7 +9678,7 @@
       <c r="A69" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="B69" s="10" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>1.5/9</t>
         </is>
@@ -9022,7 +9786,7 @@
       <c r="A70" s="5" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="11" t="inlineStr">
         <is>
           <t>1.5/10</t>
         </is>
@@ -9130,7 +9894,7 @@
       <c r="A71" s="5" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B71" s="11" t="inlineStr">
         <is>
           <t>1.5/11</t>
         </is>
@@ -9238,7 +10002,7 @@
       <c r="A72" s="5" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="10" t="inlineStr">
+      <c r="B72" s="11" t="inlineStr">
         <is>
           <t>1.5/12</t>
         </is>
@@ -9341,7 +10105,7 @@
       <c r="A73" s="5" t="n">
         <v>72</v>
       </c>
-      <c r="B73" s="10" t="inlineStr">
+      <c r="B73" s="11" t="inlineStr">
         <is>
           <t>1.5/13</t>
         </is>
@@ -9437,7 +10201,7 @@
       <c r="A74" s="5" t="n">
         <v>73</v>
       </c>
-      <c r="B74" s="10" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>1.5/14</t>
         </is>
@@ -9541,7 +10305,7 @@
       <c r="A75" s="5" t="n">
         <v>74</v>
       </c>
-      <c r="B75" s="10" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>1.5/15</t>
         </is>
@@ -9644,7 +10408,7 @@
       <c r="A76" s="5" t="n">
         <v>75</v>
       </c>
-      <c r="B76" s="10" t="inlineStr">
+      <c r="B76" s="11" t="inlineStr">
         <is>
           <t>1.5/16</t>
         </is>
@@ -9748,7 +10512,7 @@
       <c r="A77" s="5" t="n">
         <v>76</v>
       </c>
-      <c r="B77" s="10" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>1.5/17</t>
         </is>
@@ -9852,7 +10616,7 @@
       <c r="A78" s="5" t="n">
         <v>77</v>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>1.5/18</t>
         </is>
@@ -9956,7 +10720,7 @@
       <c r="A79" s="5" t="n">
         <v>78</v>
       </c>
-      <c r="B79" s="10" t="inlineStr">
+      <c r="B79" s="11" t="inlineStr">
         <is>
           <t>1.6/51</t>
         </is>
@@ -10064,7 +10828,7 @@
       <c r="A80" s="5" t="n">
         <v>79</v>
       </c>
-      <c r="B80" s="10" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>1.6/52</t>
         </is>
@@ -10172,7 +10936,7 @@
       <c r="A81" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="B81" s="10" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>1.6/53</t>
         </is>
@@ -10280,7 +11044,7 @@
       <c r="A82" s="5" t="n">
         <v>81</v>
       </c>
-      <c r="B82" s="10" t="inlineStr">
+      <c r="B82" s="11" t="inlineStr">
         <is>
           <t>1.6/54</t>
         </is>
@@ -10388,7 +11152,7 @@
       <c r="A83" s="5" t="n">
         <v>82</v>
       </c>
-      <c r="B83" s="10" t="inlineStr">
+      <c r="B83" s="11" t="inlineStr">
         <is>
           <t>1.6/55</t>
         </is>
@@ -10496,7 +11260,7 @@
       <c r="A84" s="5" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="11" t="inlineStr">
         <is>
           <t>1.6/56</t>
         </is>
@@ -10604,7 +11368,7 @@
       <c r="A85" s="5" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="11" t="inlineStr">
         <is>
           <t>1.6/57</t>
         </is>
@@ -10712,7 +11476,7 @@
       <c r="A86" s="5" t="n">
         <v>85</v>
       </c>
-      <c r="B86" s="10" t="inlineStr">
+      <c r="B86" s="11" t="inlineStr">
         <is>
           <t>1.6/58</t>
         </is>
@@ -10820,7 +11584,7 @@
       <c r="A87" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="B87" s="10" t="inlineStr">
+      <c r="B87" s="11" t="inlineStr">
         <is>
           <t>1.6/59</t>
         </is>
@@ -10928,7 +11692,7 @@
       <c r="A88" s="5" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="10" t="inlineStr">
+      <c r="B88" s="11" t="inlineStr">
         <is>
           <t>1.6/60</t>
         </is>
@@ -11036,7 +11800,7 @@
       <c r="A89" s="5" t="n">
         <v>88</v>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B89" s="11" t="inlineStr">
         <is>
           <t>1.6/61</t>
         </is>
@@ -11144,7 +11908,7 @@
       <c r="A90" s="5" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B90" s="11" t="inlineStr">
         <is>
           <t>1.6/62</t>
         </is>
@@ -11252,7 +12016,7 @@
       <c r="A91" s="5" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>1.6/63</t>
         </is>
@@ -11362,7 +12126,7 @@
       <c r="A92" s="5" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="10" t="inlineStr">
+      <c r="B92" s="11" t="inlineStr">
         <is>
           <t>1.6/64</t>
         </is>
@@ -11472,7 +12236,7 @@
       <c r="A93" s="5" t="n">
         <v>92</v>
       </c>
-      <c r="B93" s="10" t="inlineStr">
+      <c r="B93" s="11" t="inlineStr">
         <is>
           <t>1.6/65</t>
         </is>
@@ -11582,7 +12346,7 @@
       <c r="A94" s="5" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B94" s="11" t="inlineStr">
         <is>
           <t>1.6/66</t>
         </is>
@@ -11692,7 +12456,7 @@
       <c r="A95" s="5" t="n">
         <v>94</v>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B95" s="11" t="inlineStr">
         <is>
           <t>1.6/67</t>
         </is>
@@ -11802,7 +12566,7 @@
       <c r="A96" s="5" t="n">
         <v>95</v>
       </c>
-      <c r="B96" s="10" t="inlineStr">
+      <c r="B96" s="11" t="inlineStr">
         <is>
           <t>1.6/68</t>
         </is>
@@ -11910,7 +12674,7 @@
       <c r="A97" s="5" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="10" t="inlineStr">
+      <c r="B97" s="11" t="inlineStr">
         <is>
           <t>1.6/69</t>
         </is>
@@ -12018,7 +12782,7 @@
       <c r="A98" s="5" t="n">
         <v>97</v>
       </c>
-      <c r="B98" s="10" t="inlineStr">
+      <c r="B98" s="11" t="inlineStr">
         <is>
           <t>1.6/70</t>
         </is>
@@ -12126,7 +12890,7 @@
       <c r="A99" s="5" t="n">
         <v>98</v>
       </c>
-      <c r="B99" s="10" t="inlineStr">
+      <c r="B99" s="11" t="inlineStr">
         <is>
           <t>1.6/71</t>
         </is>
@@ -12237,7 +13001,7 @@
       <c r="A100" s="5" t="n">
         <v>99</v>
       </c>
-      <c r="B100" s="10" t="inlineStr">
+      <c r="B100" s="11" t="inlineStr">
         <is>
           <t>1.6/72</t>
         </is>
@@ -12348,7 +13112,7 @@
       <c r="A101" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="B101" s="10" t="inlineStr">
+      <c r="B101" s="11" t="inlineStr">
         <is>
           <t>1.6/73</t>
         </is>
@@ -12459,7 +13223,7 @@
       <c r="A102" s="5" t="n">
         <v>101</v>
       </c>
-      <c r="B102" s="10" t="inlineStr">
+      <c r="B102" s="11" t="inlineStr">
         <is>
           <t>1.6/74</t>
         </is>
@@ -12570,7 +13334,7 @@
       <c r="A103" s="5" t="n">
         <v>102</v>
       </c>
-      <c r="B103" s="10" t="inlineStr">
+      <c r="B103" s="11" t="inlineStr">
         <is>
           <t>1.6/75</t>
         </is>
@@ -12681,7 +13445,7 @@
       <c r="A104" s="5" t="n">
         <v>103</v>
       </c>
-      <c r="B104" s="10" t="inlineStr">
+      <c r="B104" s="11" t="inlineStr">
         <is>
           <t>1.6/76</t>
         </is>
@@ -12792,7 +13556,7 @@
       <c r="A105" s="5" t="n">
         <v>104</v>
       </c>
-      <c r="B105" s="10" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>1.6/77</t>
         </is>
@@ -12907,7 +13671,7 @@
       <c r="A106" s="5" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="10" t="inlineStr">
+      <c r="B106" s="11" t="inlineStr">
         <is>
           <t>1.6/78</t>
         </is>
@@ -13022,7 +13786,7 @@
       <c r="A107" s="5" t="n">
         <v>106</v>
       </c>
-      <c r="B107" s="10" t="inlineStr">
+      <c r="B107" s="11" t="inlineStr">
         <is>
           <t>1.6/79</t>
         </is>
@@ -13137,7 +13901,7 @@
       <c r="A108" s="5" t="n">
         <v>107</v>
       </c>
-      <c r="B108" s="10" t="inlineStr">
+      <c r="B108" s="11" t="inlineStr">
         <is>
           <t>1.6/80</t>
         </is>
@@ -13252,7 +14016,7 @@
       <c r="A109" s="5" t="n">
         <v>108</v>
       </c>
-      <c r="B109" s="10" t="inlineStr">
+      <c r="B109" s="11" t="inlineStr">
         <is>
           <t>1.6/81</t>
         </is>
@@ -13359,7 +14123,7 @@
       <c r="A110" s="5" t="n">
         <v>109</v>
       </c>
-      <c r="B110" s="10" t="inlineStr">
+      <c r="B110" s="11" t="inlineStr">
         <is>
           <t>1.6/82</t>
         </is>
@@ -13459,7 +14223,7 @@
       <c r="A111" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="B111" s="10" t="inlineStr">
+      <c r="B111" s="11" t="inlineStr">
         <is>
           <t>1.6/83</t>
         </is>
@@ -13562,7 +14326,7 @@
       <c r="A112" s="5" t="n">
         <v>111</v>
       </c>
-      <c r="B112" s="10" t="inlineStr">
+      <c r="B112" s="11" t="inlineStr">
         <is>
           <t>1.6/84</t>
         </is>
@@ -13665,7 +14429,7 @@
       <c r="A113" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="10" t="inlineStr">
+      <c r="B113" s="11" t="inlineStr">
         <is>
           <t>1.6/85</t>
         </is>
@@ -13768,7 +14532,7 @@
       <c r="A114" s="5" t="n">
         <v>113</v>
       </c>
-      <c r="B114" s="10" t="inlineStr">
+      <c r="B114" s="11" t="inlineStr">
         <is>
           <t>1.6/86</t>
         </is>
@@ -13871,7 +14635,7 @@
       <c r="A115" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="B115" s="10" t="inlineStr">
+      <c r="B115" s="11" t="inlineStr">
         <is>
           <t>1.6/87</t>
         </is>
@@ -13974,7 +14738,7 @@
       <c r="A116" s="5" t="n">
         <v>115</v>
       </c>
-      <c r="B116" s="10" t="inlineStr">
+      <c r="B116" s="11" t="inlineStr">
         <is>
           <t>1.6/88</t>
         </is>
@@ -14077,7 +14841,7 @@
       <c r="A117" s="5" t="n">
         <v>116</v>
       </c>
-      <c r="B117" s="10" t="inlineStr">
+      <c r="B117" s="11" t="inlineStr">
         <is>
           <t>1.7/2</t>
         </is>
@@ -14185,7 +14949,7 @@
       <c r="A118" s="5" t="n">
         <v>117</v>
       </c>
-      <c r="B118" s="10" t="inlineStr">
+      <c r="B118" s="11" t="inlineStr">
         <is>
           <t>1.7/3</t>
         </is>
@@ -14293,7 +15057,7 @@
       <c r="A119" s="5" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="10" t="inlineStr">
+      <c r="B119" s="11" t="inlineStr">
         <is>
           <t>1.7/4</t>
         </is>
@@ -14401,7 +15165,7 @@
       <c r="A120" s="5" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="10" t="inlineStr">
+      <c r="B120" s="11" t="inlineStr">
         <is>
           <t>1.8/2</t>
         </is>
@@ -14501,7 +15265,7 @@
       <c r="A121" s="5" t="n">
         <v>120</v>
       </c>
-      <c r="B121" s="10" t="inlineStr">
+      <c r="B121" s="11" t="inlineStr">
         <is>
           <t>1.8/3</t>
         </is>
@@ -14601,7 +15365,7 @@
       <c r="A122" s="5" t="n">
         <v>121</v>
       </c>
-      <c r="B122" s="10" t="inlineStr">
+      <c r="B122" s="11" t="inlineStr">
         <is>
           <t>1.8/4</t>
         </is>
@@ -14701,7 +15465,7 @@
       <c r="A123" s="5" t="n">
         <v>122</v>
       </c>
-      <c r="B123" s="10" t="inlineStr">
+      <c r="B123" s="11" t="inlineStr">
         <is>
           <t>1.8/5</t>
         </is>
@@ -14801,7 +15565,7 @@
       <c r="A124" s="5" t="n">
         <v>123</v>
       </c>
-      <c r="B124" s="10" t="inlineStr">
+      <c r="B124" s="11" t="inlineStr">
         <is>
           <t>1.8/6</t>
         </is>
@@ -14901,7 +15665,7 @@
       <c r="A125" s="5" t="n">
         <v>124</v>
       </c>
-      <c r="B125" s="10" t="inlineStr">
+      <c r="B125" s="11" t="inlineStr">
         <is>
           <t>1.8/7</t>
         </is>
@@ -15153,7 +15917,7 @@
       <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>1.1/22</t>
         </is>
@@ -15244,7 +16008,7 @@
       </c>
       <c r="U2" s="4" t="inlineStr">
         <is>
-          <t>АО «УралТехКомплектация» +7 (351) 307-71-09; ООО «ПромАрм» +7 (8412) 35-07-97; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи)</t>
+          <t>АО «УралТехКомплектация» +7 (351) 307-71-09; ООО «ПромАрм» +7 (8412) 35-07-97; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи); АО «Пензенский арматурный завод» +7 (8412) 20-11-00; ООО ПО «Нефтехимавтоматика» 8-800-350-65-67</t>
         </is>
       </c>
       <c r="V2" s="4" t="inlineStr">
@@ -15257,7 +16021,7 @@
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>1.1/23</t>
         </is>
@@ -15354,7 +16118,7 @@
       </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
-          <t>АО «УралТехКомплектация» +7 (351) 307-71-09; ООО «ПромАрм» +7 (8412) 35-07-97; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи)</t>
+          <t>АО «УралТехКомплектация» +7 (351) 307-71-09; ООО «ПромАрм» +7 (8412) 35-07-97; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи); АО «Пензенский арматурный завод» +7 (8412) 20-11-00; ООО ПО «Нефтехимавтоматика» 8-800-350-65-67</t>
         </is>
       </c>
       <c r="V3" s="4" t="inlineStr">
@@ -15367,7 +16131,7 @@
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>1.3/32</t>
         </is>
@@ -15452,7 +16216,7 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr">
         <is>
           <t>нет проверенного — искать дальше</t>
         </is>
@@ -15467,7 +16231,7 @@
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1.3/33</t>
         </is>
@@ -15552,7 +16316,7 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr">
+      <c r="U5" s="12" t="inlineStr">
         <is>
           <t>нет проверенного — искать дальше</t>
         </is>
@@ -15567,7 +16331,7 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>1.3/34</t>
         </is>
@@ -15648,7 +16412,7 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr">
+      <c r="U6" s="12" t="inlineStr">
         <is>
           <t>нет проверенного — искать дальше</t>
         </is>
@@ -15663,7 +16427,7 @@
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>1.3/150</t>
         </is>
@@ -15751,7 +16515,7 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>ООО «ПромАрм» +7 (8412) 35-07-97; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи)</t>
+          <t>ООО «ПромАрм» +7 (8412) 35-07-97; АО «Пензтяжпромарматура» 8 800 444-00-28 (продажи); АО «Пензенский арматурный завод» +7 (8412) 20-11-00; ООО «ПО БЗТпА» +7 (4832) 32-20-22</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -15916,7 +16680,7 @@
       <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>1.3/2</t>
         </is>
@@ -16012,9 +16776,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод)</t>
         </is>
       </c>
       <c r="V2" s="4" t="inlineStr">
@@ -16027,7 +16791,7 @@
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>1.3/3</t>
         </is>
@@ -16123,9 +16887,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U3" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод)</t>
         </is>
       </c>
       <c r="V3" s="4" t="inlineStr">
@@ -16138,7 +16902,7 @@
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>1.3/4</t>
         </is>
@@ -16234,9 +16998,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U4" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод)</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
@@ -16249,7 +17013,7 @@
       <c r="A5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>1.3/5</t>
         </is>
@@ -16345,9 +17109,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U5" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» +7 (4725) 469-470 (завод)</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
@@ -16360,7 +17124,7 @@
       <c r="A6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>1.3/23</t>
         </is>
@@ -16437,9 +17201,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U6" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U6" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Челябинский завод трубопроводной арматуры» +7 (351) 215-53-33; ООО «Пермский трубопроводный завод» +7 (342) 270-07-34</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
@@ -16452,7 +17216,7 @@
       <c r="A7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>1.3/24</t>
         </is>
@@ -16529,9 +17293,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U7" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U7" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Челябинский завод трубопроводной арматуры» +7 (351) 215-53-33; ООО «Пермский трубопроводный завод» +7 (342) 270-07-34</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -16544,7 +17308,7 @@
       <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>1.3/40</t>
         </is>
@@ -16633,9 +17397,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U8" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>Компания «Арматон» +7 (963) 728-59-82</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
@@ -16648,7 +17412,7 @@
       <c r="A9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>1.3/45</t>
         </is>
@@ -16741,9 +17505,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U9" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Нижегородский завод «Старт» +7 (831) 253-83-11; Компания «Арматон» +7 (963) 728-59-82</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
@@ -16756,7 +17520,7 @@
       <c r="A10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>1.3/46</t>
         </is>
@@ -16849,9 +17613,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U10" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Нижегородский завод «Старт» +7 (831) 253-83-11; Компания «Арматон» +7 (963) 728-59-82</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
@@ -16864,7 +17628,7 @@
       <c r="A11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>1.3/47</t>
         </is>
@@ -16957,9 +17721,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Нижегородский завод «Старт» +7 (831) 253-83-11; Компания «Арматон» +7 (963) 728-59-82</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
@@ -16972,7 +17736,7 @@
       <c r="A12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>1.3/56</t>
         </is>
@@ -17057,9 +17821,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U12" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» +7 (342) 270-07-34; Компания «Арматон» +7 (963) 728-59-82</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
@@ -17072,7 +17836,7 @@
       <c r="A13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>1.3/57</t>
         </is>
@@ -17157,9 +17921,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U13" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» +7 (342) 270-07-34; Компания «Арматон» +7 (963) 728-59-82</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
@@ -17172,7 +17936,7 @@
       <c r="A14" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>1.6/92</t>
         </is>
@@ -17277,9 +18041,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U14" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>ТЕД Газовые системы 8-800-550-60-80</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
@@ -17444,7 +18208,7 @@
       <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>1.1/6</t>
         </is>
@@ -17533,9 +18297,9 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="U2" s="11" t="inlineStr">
-        <is>
-          <t>нет проверенного — искать дальше</t>
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Челябинский завод трубопроводной арматуры» +7 (351) 215-53-33</t>
         </is>
       </c>
       <c r="V2" s="4" t="inlineStr">
@@ -17700,7 +18464,7 @@
       <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>1.3/163</t>
         </is>
@@ -17747,7 +18511,7 @@
       </c>
       <c r="U2" s="4" t="inlineStr">
         <is>
-          <t>АО «АБС ЗЭиМ Автоматизация» +7 (8352) 30-51-48; ООО «НПП «Промышленная автоматика» 8 (843) 558-25-28</t>
+          <t>АО «АБС ЗЭиМ Автоматизация» +7 (8352) 30-51-48; ООО «НПП «Промышленная автоматика» 8 (843) 558-25-28; ООО «Арма-Пром» +7 (4725) 469-470 (завод); ПЭК — «Поволжская Электротехническая Компания» +7 (8352) 57-05-16; ООО «Аврора» +7 (495) 956-62-18</t>
         </is>
       </c>
       <c r="V2" s="4" t="inlineStr">
@@ -17760,7 +18524,7 @@
       <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>1.4/1</t>
         </is>
@@ -17820,7 +18584,7 @@
       <c r="A4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>1.6/93</t>
         </is>
@@ -17911,7 +18675,7 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>АО «АБС ЗЭиМ Автоматизация» +7 (8352) 30-51-48</t>
+          <t>АО «АБС ЗЭиМ Автоматизация» +7 (8352) 30-51-48; Фирменный магазин ESBE 8-800-333-12-09</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">

--- a/KAMCHATKA_OPEN_ZAPROS_2710.xlsx
+++ b/KAMCHATKA_OPEN_ZAPROS_2710.xlsx
@@ -9,19 +9,20 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кому запросить" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Краны" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Затворы" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Клапаны" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задвижки" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приводы и прочее" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кандидаты без проверки" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Краны" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Затворы" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Клапаны" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задвижки" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приводы и прочее" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Кому запросить'!$A$1:$M$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Краны'!$A$1:$V$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Затворы'!$A$1:$V$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Клапаны'!$A$1:$V$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Задвижки'!$A$1:$V$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Приводы и прочее'!$A$1:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Кому запросить'!$A$1:$M$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Краны'!$A$1:$V$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Затворы'!$A$1:$V$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Клапаны'!$A$1:$V$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Задвижки'!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Приводы и прочее'!$A$1:$V$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,10 +588,10 @@
         <v>2360</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>0</v>
@@ -697,10 +698,10 @@
         <v>2413</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>3</v>
@@ -866,7 +867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1083,12 +1084,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>ЛЗТА «Маршал» (Луганский завод трубопроводной арматуры); сайт и продажи — ООО «Арматура М», официальный дистрибьютор завода</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Угрешский завод трубопроводной арматуры» (УЗТПА, ТМ «УГРЕША», серии AQUARIUS/NEON)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1098,45 +1099,45 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Луганск (ул. Монтажная, 13); склад/офис — Московская обл., г. Дзержинский, ул. Алексеевская, 5</t>
+          <t>г. Дзержинский (Московская обл.), ул. Лесная, 34</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>8 (800) 301-20-50</t>
+          <t>+7 (495) 120-57-89</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>info@lztamarshal.ru</t>
+          <t>info@uztpa.ru</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>lztamarshal.ru</t>
+          <t>https://uztpa.ru</t>
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+          <t>1.1/20, 1.1/21, 1.2/1, 1.2/2, 1.2/3, 1.2/4, 1.2/5, 1.3/106, 1.3/107, 1.3/108, 1.3/109, 1.3/110, 1.3/111, 1.3/112, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.3/127, 1.3/128, 1.3/129, 1.3/130, 1.3/131, 1.3/132, 1.3/13</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>ТОЧНЫЕ обозначения из ТЗ: «11с67п ЦУФ.00.1» (цельносварной укороченный фланцевый полнопроходной Ду15–200 Ру16/25/40) = «ЦУФ.001 КШ» в ТЗ; «10нж45фт-01 ЦУФ» и «10нж45/46/47фт-01 2ЦФ» (корпус 12Х18Н10Т,</t>
+          <t>AQUARIUS — цельносварные стальные краны для тепло/водоснабжения, PN40, до +200°C, класс «А» ГОСТ 9544: фланцевые полнопроходные DN15–300 и редуцированные DN15–300, приварные DN15–1400 (закрывает 11с67</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>Да (по тексту главной страницы): «Заключение о подтверждении производства промыш</t>
+          <t>не подтверждено (ГИСП из сессии недоступен, 403) — запросить номер реестровой за</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
-          <t>https://lztamarshal.ru/contacts/</t>
+          <t>https://uztpa.ru/contacts/ ; https://2gis.ru/moscow/firm/70000001019980425 ; https://saby.ru/profile/5056009251</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1147,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>ООО «АЛСО» (завод стальных шаровых кранов ALSO)</t>
+          <t>ЛЗТА «Маршал» (Луганский завод трубопроводной арматуры); сайт и продажи — ООО «Арматура М», официальный дистрибьютор завода</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1161,26 +1162,26 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Челябинск (ул. Складская, 1)</t>
+          <t>Луганск (ул. Монтажная, 13); склад/офис — Московская обл., г. Дзержинский, ул. Алексеевская, 5</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>8-800-444-74-74</t>
+          <t>8 (800) 301-20-50</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>info@alsoarm.ru</t>
+          <t>info@lztamarshal.ru</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>alsoarm.ru</t>
+          <t>lztamarshal.ru</t>
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -1189,17 +1190,17 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Для жидких сред: приварные полнопроходные DN15–500 (PN40 до DN65, PN25 далее) и редуцированные; фланцевые полнопроходные DN15–500 (PN40 до DN50, PN16/25 DN65+) и редуцированные (в т.ч. DN250/200 PN16 </t>
+          <t>ТОЧНЫЕ обозначения из ТЗ: «11с67п ЦУФ.00.1» (цельносварной укороченный фланцевый полнопроходной Ду15–200 Ру16/25/40) = «ЦУФ.001 КШ» в ТЗ; «10нж45фт-01 ЦУФ» и «10нж45/46/47фт-01 2ЦФ» (корпус 12Х18Н10Т,</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>Да: выписка из реестра российской промышленной продукции № 10647852 от 16.06.202</t>
+          <t>Да (по тексту главной страницы): «Заключение о подтверждении производства промыш</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>https://alsoarm.ru/contacts/</t>
+          <t>https://lztamarshal.ru/contacts/</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1210,12 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>РОБЕН (ранее БРОЕН; ТМ «Балломакс») — завод в Коломне</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Уральский завод трубопроводной арматуры» (УЗТА)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1224,45 +1225,45 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Московская обл., г. Коломна, с. Нижнее Хорошово, ул. Николая Птицына, 42</t>
+          <t>г. Челябинск, ул. Рылеева, 20</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 228-11-50</t>
+          <t>+7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>info@robenvalves.ru</t>
+          <t>uzta@mail.ru</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>robenvalves.ru (broen.ru → редирект)</t>
+          <t>https://uzta74.ru</t>
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
+          <t>1.1/20, 1.1/21, 1.2/1, 1.2/2, 1.2/3, 1.2/4, 1.2/5, 1.3/106, 1.3/107, 1.3/108, 1.3/109, 1.3/110, 1.3/111, 1.3/112, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.3/127, 1.3/128, 1.3/129, 1.3/130, 1.3/131, 1.3/132, 1.3/13</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Каталог «Балломакс» КШТ 60/61 (DE_catalog_2026_09.pdf): сварка/сварка станд. DN10–1400 и полнопроходные DN15–1400; фланец/фланец станд. DN15–900 и полнопроходные DN15–1000 (PN16/25/40); резьба/резьба </t>
+          <t>Изготовитель цельносварных шаровых кранов из ст.20/09Г2С и коррозионностойкой стали: фланцевые, приварные, муфтовые, штуцерные, под привод. Нерж. 12Х18Н10Т Ду15–250 Ру16–63 (закрывает 10нж45фт 2ЦФ Ду2</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Да (по тексту https://robenvalves.ru/abouthtml): «Продукция РОБЕН производится в</t>
+          <t>не подтверждено — запросить</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>https://robenvalves.ru/contacts</t>
+          <t>https://uzta74.ru/kontakty/ ; https://2gis.ru/chelyabinsk/firm/2111590608291686 ; https://uzta74.ru/docs/uzta2019-fin.pdf</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1273,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>ООО «Краны Балашихи» (КБ)</t>
+          <t>ООО «АЛСО» (завод стальных шаровых кранов ALSO)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1287,26 +1288,26 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Балашиха, Московская обл. (ул. 1 Мая, 10Б, мкр. Саввино)</t>
+          <t>Челябинск (ул. Складская, 1)</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888)</t>
+          <t>8-800-444-74-74</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>sales@kb-arm.ru</t>
+          <t>info@alsoarm.ru</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>kb-arm.ru</t>
+          <t>alsoarm.ru</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -1315,17 +1316,17 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Приварные стандартнопроходные Ду15–200 (Ру40 до Ду50, Ру25 далее) → все «11с67п цельносварной под приварку»; фланцевые стандартнопроходные Ду15–200 и полнопроходные Ду15–125 (Ру40/16/25) → 11с22п, 11С</t>
+          <t xml:space="preserve">Для жидких сред: приварные полнопроходные DN15–500 (PN40 до DN65, PN25 далее) и редуцированные; фланцевые полнопроходные DN15–500 (PN40 до DN50, PN16/25 DN65+) и редуцированные (в т.ч. DN250/200 PN16 </t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>не найдено (на сайте kb-arm.ru упоминания записи в реестре Минпромторга не найде</t>
+          <t>Да: выписка из реестра российской промышленной продукции № 10647852 от 16.06.202</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>https://kb-arm.ru/contacts/</t>
+          <t>https://alsoarm.ru/contacts/</t>
         </is>
       </c>
     </row>
@@ -1335,60 +1336,60 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Компания «Арматон»</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>новый (исследование 27.10)</t>
+          <t>РОБЕН (ранее БРОЕН; ТМ «Балломакс») — завод в Коломне</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>дистрибьютор</t>
+          <t>завод</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Москва (Новая Москва)</t>
+          <t>Московская обл., г. Коломна, с. Нижнее Хорошово, ул. Николая Птицына, 42</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>+7 (963) 728-59-82</t>
+          <t>+7 (495) 228-11-50</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>armaton@bk.ru</t>
+          <t>info@robenvalves.ru</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>http://armaton.ru</t>
+          <t>robenvalves.ru (broen.ru → редирект)</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>1.3/40, 1.3/45, 1.3/46, 1.3/47, 1.3/56, 1.3/57</t>
+          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Узкий профиль: сильфонная и вакуумная арматура с 2002 г. В номенклатуре: 22Б16п и 22Б17п (латунные сильфонные хладоновые, редкая позиция 1.3/40), 14нж17ст / 14нж19п (сильфонные нерж., как вариант 14нж</t>
+          <t xml:space="preserve">Каталог «Балломакс» КШТ 60/61 (DE_catalog_2026_09.pdf): сварка/сварка станд. DN10–1400 и полнопроходные DN15–1400; фланец/фланец станд. DN15–900 и полнопроходные DN15–1000 (PN16/25/40); резьба/резьба </t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>Да (по тексту https://robenvalves.ru/abouthtml): «Продукция РОБЕН производится в</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>http://armaton.ru/kontakty ; http://armaton.ru/</t>
+          <t>https://robenvalves.ru/contacts</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1399,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>новый (исследование 27.10)</t>
+          <t>ООО «Краны Балашихи» (КБ)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1413,45 +1414,45 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Старый Оскол (Белгородская обл.); офис продаж — Москва</t>
+          <t>Балашиха, Московская обл. (ул. 1 Мая, 10Б, мкр. Саввино)</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>+7 (4725) 469-470 (завод)</t>
+          <t>+7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888)</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>zavod@saz-avangard.ru</t>
+          <t>sales@kb-arm.ru</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>https://saz-avangard.ru</t>
+          <t>kb-arm.ru</t>
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>5</v>
+        <v>89</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>1.3/2, 1.3/3, 1.3/4, 1.3/5, 1.3/163</t>
+          <t>1.1/20, 1.2/1, 1.2/2, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.5/12, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.5/18, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4, 1.2/3, 1.2/4, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.6/71, 1.6/72, 1.6/73, 1.6/74, 1.6/7</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Собственное производство 25ч945п: чугунный фланцевый односедельный клапан, Ду15–300, Ру16, t −15…+150 °C, ТУ 3722-…, комплектуется российским ЭИМ ПЭП-САЗ (стандарт/IN/Ex). Ду15/25/50/80 есть в каталог</t>
+          <t>Приварные стандартнопроходные Ду15–200 (Ру40 до Ду50, Ру25 далее) → все «11с67п цельносварной под приварку»; фланцевые стандартнопроходные Ду15–200 и полнопроходные Ду15–125 (Ру40/16/25) → 11с22п, 11С</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ДА: Заключение Минпромторга о подтверждении производства в РФ (ПП 719), заявлени</t>
+          <t>не найдено (на сайте kb-arm.ru упоминания записи в реестре Минпромторга не найде</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>https://saz-avangard.ru/contacts/ ; https://saz-avangard.ru/catalog/klapany-reg/odnosedelniy-chugunniy-eim/25ch945p/ ; https://saz-avangard.ru/upload/iblock/8f1/i8qtd4llupat9fpta48v2vwrbz2fj2sn/Zaklyu</t>
+          <t>https://kb-arm.ru/contacts/</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1462,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+          <t>ООО «ГАЛЛОП» (Новосибирский арматурный завод)</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1476,45 +1477,45 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Пермь</t>
+          <t>г. Новосибирск, ул. Оловозаводская, 47/8</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>+7 (342) 270-07-34</t>
+          <t>+7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>sales@ptza.ru</t>
+          <t>info@gallop.ru</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptza.ru</t>
+          <t>https://gallop.ru</t>
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>1.3/56, 1.3/57, 1.3/23, 1.3/24</t>
+          <t>1.1/14, 1.1/15, 1.1/16, 1.1/17, 1.1/18, 1.1/19, 1.3/101, 1.3/102, 1.3/103, 1.3/104, 1.3/105, 1.5/4, 1.5/5, 1.5/6, 1.5/7, 1.5/8, 1.6/51, 1.6/52, 1.6/53, 1.6/54, 1.6/55, 1.6/56</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>15нж65нж: фланцевый, Ду10–200 (есть Ду125 и Ду150), Ру1,6 МПа, корпус 12Х18Н9ТЛ / 08Х18Н10Т. 16нж10нж: подъёмный обратный, Ду10–200 (Ду32 — L180 мм, Ду50 — L230 мм), Ру1,6 МПа, корпус 08Х18Н10/12Х18Н9</t>
+          <t>Латунные шаровые краны (горячая штамповка) СТАНДАРТ/КРЕПЫШ: Ду15–25 PN40, Ду32–50 PN16, В-В/В-Н, рукоятка/бабочка — закрывает все 22 позиции 11б27п1 Ду15–50. Склад в Новосибирске, ближе всех к ДВ сред</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>не подтверждено — запросить</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptza.ru/kontakty/ ; https://www.ptza.ru/15nzh65nzh-klapan-zapornyj/ ; https://www.ptza.ru/16nzh10nzh-klapan-obratnyj-podemnyj/</t>
+          <t>https://gallop.ru/contacts/ ; https://gallop.ru/download/?file=Price.xls ; https://xn--b1aedfedwrdfl5a6k.xn--p1ai/producer/gallop</t>
         </is>
       </c>
     </row>
@@ -1524,60 +1525,60 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>ООО «ПромАрм» (PromArm®)</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>Компания «Арматон»</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>завод</t>
+          <t>дистрибьютор</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>г. Пенза, ул. Баумана, 101В (производство); офис Москва, Пресненская наб., 12</t>
+          <t>Москва (Новая Москва)</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>+7 (8412) 35-07-97</t>
+          <t>+7 (963) 728-59-82</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>info@promarm.ru</t>
+          <t>armaton@bk.ru</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>https://www.promarm.com (promarm.ru — из среды не открылся)</t>
+          <t>http://armaton.ru</t>
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>1.1/23, 1.1/22, 1.3/150</t>
+          <t>1.3/40, 1.3/45, 1.3/46, 1.3/47, 1.3/56, 1.3/57</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Держатель марки ПА954: в каталоге есть ровно «ПА954.450.10-05» — трёхэксцентриковый межфланцевый с гладкими проушинами, корпус и диск нерж. сталь с молибденом (CF8M), седло PTFE, DN450 PN10 (1.1/23 — </t>
+          <t>Узкий профиль: сильфонная и вакуумная арматура с 2002 г. В номенклатуре: 22Б16п и 22Б17п (латунные сильфонные хладоновые, редкая позиция 1.3/40), 14нж17ст / 14нж19п (сильфонные нерж., как вариант 14нж</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>не найдено (в разделе «Документы, сертификаты» — ТР ТС 032, сертификат РМРС, гиг</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>https://www.promarm.com/contacts/</t>
+          <t>http://armaton.ru/kontakty ; http://armaton.ru/</t>
         </is>
       </c>
     </row>
@@ -1587,12 +1588,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1602,45 +1603,45 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>г. Пенза (промкомплекс 225 000 м²)</t>
+          <t>Старый Оскол (Белгородская обл.); офис продаж — Москва</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>8 800 444-00-28 (продажи)</t>
+          <t>+7 (4725) 469-470 (завод)</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>sales@ptpa.ru</t>
+          <t>zavod@saz-avangard.ru</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>https://ptpa.ru</t>
+          <t>https://saz-avangard.ru</t>
         </is>
       </c>
       <c r="I12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>1.3/150, 1.1/23, 1.1/22</t>
+          <t>1.3/2, 1.3/3, 1.3/4, 1.3/5, 1.3/163</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Затворы дисковые поворотные стальные DN400–2000 PN0,25–1,6 МПа (ПТ99052-500ТУ, ГОСТ 13547-2015) и трёхэксцентриковые DN50–2000 PN1,6–4,0 МПа (ТУ3742-038-05749375-2007), нерж. исполнение до +550 °C — а</t>
+          <t>Собственное производство 25ч945п: чугунный фланцевый односедельный клапан, Ду15–300, Ру16, t −15…+150 °C, ТУ 3722-…, комплектуется российским ЭИМ ПЭП-САЗ (стандарт/IN/Ex). Ду15/25/50/80 есть в каталог</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>не найдено на сайте</t>
+          <t>ДА: Заключение Минпромторга о подтверждении производства в РФ (ПП 719), заявлени</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>https://ptpa.ru/contacts/</t>
+          <t>https://saz-avangard.ru/contacts/ ; https://saz-avangard.ru/catalog/klapany-reg/odnosedelniy-chugunniy-eim/25ch945p/ ; https://saz-avangard.ru/upload/iblock/8f1/i8qtd4llupat9fpta48v2vwrbz2fj2sn/Zaklyu</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1651,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ООО «Челябинский завод трубопроводной арматуры» (ООО «ЧЗТА», бренд «ЧЗТА АРМАКОМ»)</t>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1665,35 +1666,35 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Челябинск</t>
+          <t>Пермь</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 215-53-33</t>
+          <t>+7 (342) 270-07-34</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>zakaz@chzta.ru</t>
+          <t>sales@ptza.ru</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>https://chzta.ru</t>
+          <t>https://www.ptza.ru</t>
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>1.1/6, 1.3/23, 1.3/24</t>
+          <t>1.3/56, 1.3/57, 1.3/23, 1.3/24</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>1.1/6: в каталоге есть именно «Задвижка нержавеющая 30нж947нж Ду1000 Ру4», сталь 12Х18Н10Т, фланцевая, под электропривод, масса 1085 кг, класс А, под заказ, «по ГОСТ и чертежам Заказчика». Присоединен</t>
+          <t>15нж65нж: фланцевый, Ду10–200 (есть Ду125 и Ду150), Ру1,6 МПа, корпус 12Х18Н9ТЛ / 08Х18Н10Т. 16нж10нж: подъёмный обратный, Ду10–200 (Ду32 — L180 мм, Ду50 — L230 мм), Ру1,6 МПа, корпус 08Х18Н10/12Х18Н9</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1703,7 +1704,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>https://chzta.ru/contacts/ ; https://chzta.ru/catalog/30nzh947nzh/zadvizhka-nerzhaveyushchaya-du-1000-ru-4-30nzh947nzh/ ; https://chzta.ru/upload/download/company_details.pdf</t>
+          <t>https://www.ptza.ru/kontakty/ ; https://www.ptza.ru/15nzh65nzh-klapan-zapornyj/ ; https://www.ptza.ru/16nzh10nzh-klapan-obratnyj-podemnyj/</t>
         </is>
       </c>
     </row>
@@ -1713,12 +1714,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ООО «Нижегородский завод «Старт»</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>новый (исследование 27.10)</t>
+          <t>ООО «ПромАрм» (PromArm®)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1728,22 +1729,22 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Нижний Новгород</t>
+          <t>г. Пенза, ул. Баумана, 101В (производство); офис Москва, Пресненская наб., 12</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+7 (831) 253-83-11</t>
+          <t>+7 (8412) 35-07-97</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>start.nn@mail.ru</t>
+          <t>info@promarm.ru</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>https://start-nn.ru</t>
+          <t>https://www.promarm.com (promarm.ru — из среды не открылся)</t>
         </is>
       </c>
       <c r="I14" s="5" t="n">
@@ -1751,22 +1752,22 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>1.3/45, 1.3/46, 1.3/47</t>
+          <t>1.1/23, 1.1/22, 1.3/150</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Собственный выпуск сильфонных клапанов 14нж17п / 14нж17ст / 14с17п. Штуцерно-торцевые исполнения: 14нж17п28, 14нж017п31, 14нж917п34 (по сути цапковые), Ду10–150 Ру10. 14нж17п Ду15/25/32 Ру10 нерж. с у</t>
+          <t xml:space="preserve">Держатель марки ПА954: в каталоге есть ровно «ПА954.450.10-05» — трёхэксцентриковый межфланцевый с гладкими проушинами, корпус и диск нерж. сталь с молибденом (CF8M), седло PTFE, DN450 PN10 (1.1/23 — </t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>не найдено (в разделе «Документы, сертификаты» — ТР ТС 032, сертификат РМРС, гиг</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>https://start-nn.ru/contacts/ ; https://start-nn.ru/production/bellows/</t>
+          <t>https://www.promarm.com/contacts/</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1777,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>АО «Пензенский арматурный завод» (АО «ПАЗ»)</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>новый (исследование 27.10)</t>
+          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1791,22 +1792,22 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Пенза</t>
+          <t>г. Пенза (промкомплекс 225 000 м²)</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>+7 (8412) 20-11-00</t>
+          <t>8 800 444-00-28 (продажи)</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>info@armpaz.ru</t>
+          <t>sales@ptpa.ru</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://armatura-paz.ru</t>
+          <t>https://ptpa.ru</t>
         </is>
       </c>
       <c r="I15" s="5" t="n">
@@ -1814,22 +1815,22 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>1.3/150, 1.1/22, 1.1/23</t>
+          <t>1.3/150, 1.1/23, 1.1/22</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Дисковые затворы производства АО «ПАЗ», в том числе трёхэксцентриковые: DN50–2000, межфланцевые, фланцевые, под приварку; корпус и диск могут быть нержавеющими; привод — редуктор, электро- или пневмоп</t>
+          <t>Затворы дисковые поворотные стальные DN400–2000 PN0,25–1,6 МПа (ПТ99052-500ТУ, ГОСТ 13547-2015) и трёхэксцентриковые DN50–2000 PN1,6–4,0 МПа (ТУ3742-038-05749375-2007), нерж. исполнение до +550 °C — а</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>не найдено (на сайте не указано)</t>
+          <t>не найдено на сайте</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>https://armatura-paz.ru/contacts ; https://armatura-paz.ru/catalog/obshchepromyshlennaya-armatura/diskovye-zatvory</t>
+          <t>https://ptpa.ru/contacts/</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1840,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Челябинский завод трубопроводной арматуры» (ООО «ЧЗТА», бренд «ЧЗТА АРМАКОМ»)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1854,45 +1855,45 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Челябинская обл., г. Озёрск, ул. Индустриальная, 4</t>
+          <t>Челябинск</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>+7 (351) 307-71-09</t>
+          <t>+7 (351) 215-53-33</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>info@aoutk.ru</t>
+          <t>zakaz@chzta.ru</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://aoutk.ru</t>
+          <t>https://chzta.ru</t>
         </is>
       </c>
       <c r="I16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>1.1/22, 1.1/23</t>
+          <t>1.1/6, 1.3/23, 1.3/24</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>MV UBZ1 межфланцевый с эластомерным седлом: DN25–600, PN6/10/16/25, корпус GGG40 / WCB / CF8 / CF8M, верхний фланец ISO 5211, класс А — закрывает чугунные межфланцевые Ду65–200 Ру16 и как аналог Stens</t>
+          <t>1.1/6: в каталоге есть именно «Задвижка нержавеющая 30нж947нж Ду1000 Ру4», сталь 12Х18Н10Т, фланцевая, под электропривод, масса 1085 кг, класс А, под заказ, «по ГОСТ и чертежам Заказчика». Присоединен</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>не найдено (на странице сертификатов — только декларации ЕАЭС ТР ТС 010/032)</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>https://aoutk.ru/contacts</t>
+          <t>https://chzta.ru/contacts/ ; https://chzta.ru/catalog/30nzh947nzh/zadvizhka-nerzhaveyushchaya-du-1000-ru-4-30nzh947nzh/ ; https://chzta.ru/upload/download/company_details.pdf</t>
         </is>
       </c>
     </row>
@@ -1902,12 +1903,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>АО «АБС ЗЭиМ Автоматизация»</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО «Нижегородский завод «Старт»</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1917,45 +1918,45 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>г. Чебоксары, пр-т И. Яковлева, 1</t>
+          <t>Нижний Новгород</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>+7 (8352) 30-51-48</t>
+          <t>+7 (831) 253-83-11</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>sales@zeim.ru</t>
+          <t>start.nn@mail.ru</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.zeim.ru</t>
+          <t>https://start-nn.ru</t>
         </is>
       </c>
       <c r="I17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>1.3/163, 1.6/93</t>
+          <t>1.3/45, 1.3/46, 1.3/47</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Аналог Regada ST0 490.0 (1.3/163): прямоходные МЭПК-800/1600/2500-99 (усилие 800/1600/2500 Н, ход 20/40 мм, 220/230/240 В, IP54/65, У1…УХЛ1) — подобрать по усилию/ходу клапана. Аналог ESBE 95 (1.6/93,</t>
+          <t>Собственный выпуск сильфонных клапанов 14нж17п / 14нж17ст / 14с17п. Штуцерно-торцевые исполнения: 14нж17п28, 14нж017п31, 14нж917п34 (по сути цапковые), Ду10–150 Ру10. 14нж17п Ду15/25/32 Ру10 нерж. с у</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>не найдено на сайте</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>https://www.zeim.ru/contacts/</t>
+          <t>https://start-nn.ru/contacts/ ; https://start-nn.ru/production/bellows/</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1966,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ООО ПО «Нефтехимавтоматика» (НХА)</t>
+          <t>АО «Пензенский арматурный завод» (АО «ПАЗ»)</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1980,45 +1981,45 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Москва (офис); производство — г. Киреевск, Тульская обл., ул. Тесакова, 9-Г</t>
+          <t>Пенза</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>8-800-350-65-67</t>
+          <t>+7 (8412) 20-11-00</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>zakaz@nhavtomatika.ru</t>
+          <t>info@armpaz.ru</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://nhavtomatika.ru</t>
+          <t>https://armatura-paz.ru</t>
         </is>
       </c>
       <c r="I18" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>1.1/22, 1.1/23</t>
+          <t>1.3/150, 1.1/22, 1.1/23</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Трёхэксцентриковые затворы НХА-7: DN50–1200, PN10–100. Межфланцевое (МФ), фланцевое и приварное исполнения. Корпус и диск: 08Х18Н10 (CF8) или 10Х17Н13М2Т (CF8M). Уплотнение — шихтованное 12Х18Н10 + гр</t>
+          <t>Дисковые затворы производства АО «ПАЗ», в том числе трёхэксцентриковые: DN50–2000, межфланцевые, фланцевые, под приварку; корпус и диск могут быть нержавеющими; привод — редуктор, электро- или пневмоп</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>не найдено (на сайте не указано)</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>https://nhavtomatika.ru/contacts/ ; https://nhavtomatika.ru/catalog_self/truboprovodnaya_armatura/zatvory/zatvory_disk_treh_flanc_pnevmoprivod/</t>
+          <t>https://armatura-paz.ru/contacts ; https://armatura-paz.ru/catalog/obshchepromyshlennaya-armatura/diskovye-zatvory</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2029,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
+          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2043,45 +2044,45 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Рыбинск (Ярославская обл.)</t>
+          <t>Челябинская обл., г. Озёрск, ул. Индустриальная, 4</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>8-800-700-62-60</t>
+          <t>+7 (351) 307-71-09</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>info@fobosarm.ru</t>
+          <t>info@aoutk.ru</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>fobosarm.ru</t>
+          <t>https://aoutk.ru</t>
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>1.3/135</t>
+          <t>1.1/22, 1.1/23</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Кран шаровый муфтовый Ду6–50, Ру до 6,3 МПа; корпус 1.4408 (литьё, аналог CF8M/AISI 316 ≈ 08Х17Н13М2) или 12Х18Н9ТЛ/12Х18Н10Т; седло фторопласт Ф4; серии МОНО/ЭКОНОМ/РЕТРО. ВНИМАНИЕ: на сайте температ</t>
+          <t>MV UBZ1 межфланцевый с эластомерным седлом: DN25–600, PN6/10/16/25, корпус GGG40 / WCB / CF8 / CF8M, верхний фланец ISO 5211, класс А — закрывает чугунные межфланцевые Ду65–200 Ру16 и как аналог Stens</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>не найдено (запросить у завода)</t>
+          <t>не найдено (на странице сертификатов — только декларации ЕАЭС ТР ТС 010/032)</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>https://fobosarm.ru/contacts/</t>
+          <t>https://aoutk.ru/contacts</t>
         </is>
       </c>
     </row>
@@ -2091,7 +2092,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>ООО «НПП «Промышленная автоматика» (НПП «ПРОМА»)</t>
+          <t>АО «АБС ЗЭиМ Автоматизация»</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -2106,45 +2107,45 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>г. Казань, ул. Г. Тукая, 125к6 (фактический адрес)</t>
+          <t>г. Чебоксары, пр-т И. Яковлева, 1</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>8 (843) 558-25-28</t>
+          <t>+7 (8352) 30-51-48</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>info@promav.ru</t>
+          <t>sales@zeim.ru</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://www.promav.ru</t>
+          <t>https://www.zeim.ru</t>
         </is>
       </c>
       <c r="I20" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>1.3/163</t>
+          <t>1.3/163, 1.6/93</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>МЭП-М (механизм электрический исполнительный прямоходный, ТУ 4218-033-04880601-2004), исполнения 800/30-220, 1600/45-400, 5000/60-530 — аналог Regada ST0. Страница о производстве без описания цехов; д</t>
+          <t>Аналог Regada ST0 490.0 (1.3/163): прямоходные МЭПК-800/1600/2500-99 (усилие 800/1600/2500 Н, ход 20/40 мм, 220/230/240 В, IP54/65, У1…УХЛ1) — подобрать по усилию/ходу клапана. Аналог ESBE 95 (1.6/93,</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>не найдено на сайте</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>https://www.promav.ru/contacts/</t>
+          <t>https://www.zeim.ru/contacts/</t>
         </is>
       </c>
     </row>
@@ -2154,12 +2155,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>ООО «ПКФ «ТЕРМ»</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>известный</t>
+          <t>ООО ПО «Нефтехимавтоматика» (НХА)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -2169,35 +2170,35 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>г. Саратов, ул. Танкистов, 195</t>
+          <t>Москва (офис); производство — г. Киреевск, Тульская обл., ул. Тесакова, 9-Г</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>+7 (927) 279-09-83</t>
+          <t>8-800-350-65-67</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>term1998@yandex.ru</t>
+          <t>zakaz@nhavtomatika.ru</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://pkfterm.ru</t>
+          <t>https://nhavtomatika.ru</t>
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>1.4/1</t>
+          <t>1.1/22, 1.1/23</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>«Специализируется на производстве рыбозащитных оголовков с потокообразователем (РОП) моделей СРО и СРБ»; тип РЗУ — «жалюзийный экран с потокообразователем» по СП 101.13330.2023; СРО-20…350 (до 0,35 м³</t>
+          <t>Трёхэксцентриковые затворы НХА-7: DN50–1200, PN10–100. Межфланцевое (МФ), фланцевое и приварное исполнения. Корпус и диск: 08Х18Н10 (CF8) или 10Х17Н13М2Т (CF8M). Уплотнение — шихтованное 12Х18Н10 + гр</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2207,7 +2208,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>https://pkfterm.ru/ (блок «Контактная информация»; сайт одностраничный)</t>
+          <t>https://nhavtomatika.ru/contacts/ ; https://nhavtomatika.ru/catalog_self/truboprovodnaya_armatura/zatvory/zatvory_disk_treh_flanc_pnevmoprivod/</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2218,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>ООО «Регул»</t>
+          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2232,22 +2233,22 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>г. Чебоксары, пр-д Машиностроителей, 1 (территория ОАО «Текстильмаш») — производство; офис Москва</t>
+          <t>Рыбинск (Ярославская обл.)</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>+7 (499) 653-65-06</t>
+          <t>8-800-700-62-60</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>regyl21@mail.ru</t>
+          <t>info@fobosarm.ru</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://regul21.ru</t>
+          <t>fobosarm.ru</t>
         </is>
       </c>
       <c r="I22" s="5" t="n">
@@ -2255,22 +2256,22 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>1.4/1</t>
+          <t>1.3/135</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Рыбозащитный оголовок с потокообразователем РОП (перфорированный конус; расход потокообразователя 7 %, напор 30 м; до 85…1050 м³/ч), изготовление нестандартных размеров по ТЗ/чертежам заказчика.</t>
+          <t>Кран шаровый муфтовый Ду6–50, Ру до 6,3 МПа; корпус 1.4408 (литьё, аналог CF8M/AISI 316 ≈ 08Х17Н13М2) или 12Х18Н9ТЛ/12Х18Н10Т; седло фторопласт Ф4; серии МОНО/ЭКОНОМ/РЕТРО. ВНИМАНИЕ: на сайте температ</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>не найдено</t>
+          <t>не найдено (запросить у завода)</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>https://regul21.ru/contacts</t>
+          <t>https://fobosarm.ru/contacts/</t>
         </is>
       </c>
     </row>
@@ -2280,12 +2281,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ПЭК — «Поволжская Электротехническая Компания» (сайт piek.ru)</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>новый (исследование 27.10)</t>
+          <t>ООО «НПП «Промышленная автоматика» (НПП «ПРОМА»)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -2295,22 +2296,22 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Чебоксары</t>
+          <t>г. Казань, ул. Г. Тукая, 125к6 (фактический адрес)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>+7 (8352) 57-05-16</t>
+          <t>8 (843) 558-25-28</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>info@piek.ru</t>
+          <t>info@promav.ru</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>https://piek.ru</t>
+          <t>https://www.promav.ru</t>
         </is>
       </c>
       <c r="I23" s="5" t="n">
@@ -2323,7 +2324,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Российский аналог Regada ST0 490.0 — прямоходный МЭП-2500: усилие 2500 Н, ходы 10/20/30/60 мм, 220/380 В, IP65/67, блок БКВ с токовым датчиком 4–20 мА. По ТЗ нужен ход 25 мм (ближайший — 30 мм) и скор</t>
+          <t>МЭП-М (механизм электрический исполнительный прямоходный, ТУ 4218-033-04880601-2004), исполнения 800/30-220, 1600/45-400, 5000/60-530 — аналог Regada ST0. Страница о производстве без описания цехов; д</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2333,7 +2334,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>https://piek.ru/contacts/ ; https://piek.ru/mechanisms-mep/2500/</t>
+          <t>https://www.promav.ru/contacts/</t>
         </is>
       </c>
     </row>
@@ -2343,37 +2344,37 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ТЕД Газовые системы (TEDGAS; сервисный центр DUNGS; домен dungs.ru ведёт на tedgas.ru)</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>новый (исследование 27.10)</t>
+          <t>ООО «ПКФ «ТЕРМ»</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>дистрибьютор</t>
+          <t>завод</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Москва</t>
+          <t>г. Саратов, ул. Танкистов, 195</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>8-800-550-60-80</t>
+          <t>+7 (927) 279-09-83</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>info@tedgas.ru (отдел продаж: retail@karldungs.ru)</t>
+          <t>term1998@yandex.ru</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>https://tedgas.ru</t>
+          <t>https://pkfterm.ru</t>
         </is>
       </c>
       <c r="I24" s="5" t="n">
@@ -2381,22 +2382,22 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>1.6/92</t>
+          <t>1.4/1</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">В каталоге есть ровно артикул из ТЗ: DUNGS LGV 507/5 230 VAC IP54, арт. 119271 (по каталогу это нормально открытый, сбросной клапан). Компанию основали бывшие сотрудники представительства Karl Dungs; </t>
+          <t>«Специализируется на производстве рыбозащитных оголовков с потокообразователем (РОП) моделей СРО и СРБ»; тип РЗУ — «жалюзийный экран с потокообразователем» по СП 101.13330.2023; СРО-20…350 (до 0,35 м³</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>нет (импорт DUNGS, Германия)</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>https://tedgas.ru/kontakti ; https://tedgas.ru/catalog/elektromagnitnie_klapani-3/lgv_elektromagnitny_klapan_normalno_otkrity-23</t>
+          <t>https://pkfterm.ru/ (блок «Контактная информация»; сайт одностраничный)</t>
         </is>
       </c>
     </row>
@@ -2406,37 +2407,37 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Фирменный магазин ESBE (esbeshop.ru)</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>новый (исследование 27.10)</t>
+          <t>ООО «Регул»</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>известный</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>дистрибьютор</t>
+          <t>завод</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Москва, ул. Кантемировская, 58</t>
+          <t>г. Чебоксары, пр-д Машиностроителей, 1 (территория ОАО «Текстильмаш») — производство; офис Москва</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>8-800-333-12-09</t>
+          <t>+7 (499) 653-65-06</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>info@esbeshop.ru</t>
+          <t>regyl21@mail.ru</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>https://esbeshop.ru</t>
+          <t>https://regul21.ru</t>
         </is>
       </c>
       <c r="I25" s="5" t="n">
@@ -2444,22 +2445,22 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>1.6/93</t>
+          <t>1.4/1</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Точный артикул ESBE 95, 12051900 (230 В, 15 Н·м, 3-точечный, 30–180°, 60 с/90°), «Есть в наличии». Производство — Швеция (импорт). Российский аналог (Ридан AMB) уже в списке известных.</t>
+          <t>Рыбозащитный оголовок с потокообразователем РОП (перфорированный конус; расход потокообразователя 7 %, напор 30 м; до 85…1050 м³/ч), изготовление нестандартных размеров по ТЗ/чертежам заказчика.</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>нет (импорт, Швеция)</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>https://esbeshop.ru/contacts ; https://esbeshop.ru/elektricheskij-privod-povorotnyj-3-tochechnyj-esbe-95-220v-15nm-30-180-60sek-90-ko</t>
+          <t>https://regul21.ru/contacts</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2470,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ООО «Аврора» (avrora-arm.ru)</t>
+          <t>ПЭК — «Поволжская Электротехническая Компания» (сайт piek.ru)</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2479,27 +2480,27 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>дистрибьютор</t>
+          <t>завод</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Москва, ул. Зеленодольская, д. 3</t>
+          <t>Чебоксары</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>+7 (495) 956-62-18</t>
+          <t>+7 (8352) 57-05-16</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>sales@avrora-arm.ru</t>
+          <t>info@piek.ru</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>https://avrora-arm.ru</t>
+          <t>https://piek.ru</t>
         </is>
       </c>
       <c r="I26" s="5" t="n">
@@ -2512,17 +2513,17 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">В каталоге прямоходные приводы REGADA серии Standard (ST 0, ST 0.1, ST 2, MTR), то есть поставка оригинала ST0 490.0-00TQV/00. Статус официального дистрибьютора на сайте не заявлен. Оригинал — импорт </t>
+          <t>Российский аналог Regada ST0 490.0 — прямоходный МЭП-2500: усилие 2500 Н, ходы 10/20/30/60 мм, 220/380 В, IP65/67, блок БКВ с токовым датчиком 4–20 мА. По ТЗ нужен ход 25 мм (ближайший — 30 мм) и скор</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>нет (импорт REGADA, Словакия)</t>
+          <t>не найдено</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>https://avrora-arm.ru/contact-us/ ; https://avrora-arm.ru/produkcziya/elektroprivodyi/regada/pryamoxodnyie/standard/elektroprivod-pryamoxodnyij-st-2-regada.html</t>
+          <t>https://piek.ru/contacts/ ; https://piek.ru/mechanisms-mep/2500/</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2533,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ООО «ПО БЗТпА» (Брянский завод трубопроводной арматуры, bztpa.ru)</t>
+          <t>ТЕД Газовые системы (TEDGAS; сервисный центр DUNGS; домен dungs.ru ведёт на tedgas.ru)</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2547,22 +2548,22 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Москва (юр. адрес); склад готовой продукции — Брянск, Московский пр-д, 29</t>
+          <t>Москва</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>+7 (4832) 32-20-22</t>
+          <t>8-800-550-60-80</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>info@bztpa.ru</t>
+          <t>info@tedgas.ru (отдел продаж: retail@karldungs.ru)</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>https://bztpa.ru</t>
+          <t>https://tedgas.ru</t>
         </is>
       </c>
       <c r="I27" s="5" t="n">
@@ -2570,33 +2571,768 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
+          <t>1.6/92</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В каталоге есть ровно артикул из ТЗ: DUNGS LGV 507/5 230 VAC IP54, арт. 119271 (по каталогу это нормально открытый, сбросной клапан). Компанию основали бывшие сотрудники представительства Karl Dungs; </t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>нет (импорт DUNGS, Германия)</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>https://tedgas.ru/kontakti ; https://tedgas.ru/catalog/elektromagnitnie_klapani-3/lgv_elektromagnitny_klapan_normalno_otkrity-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Фирменный магазин ESBE (esbeshop.ru)</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Москва, ул. Кантемировская, 58</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>8-800-333-12-09</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>info@esbeshop.ru</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>https://esbeshop.ru</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>1.6/93</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Точный артикул ESBE 95, 12051900 (230 В, 15 Н·м, 3-точечный, 30–180°, 60 с/90°), «Есть в наличии». Производство — Швеция (импорт). Российский аналог (Ридан AMB) уже в списке известных.</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>нет (импорт, Швеция)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>https://esbeshop.ru/contacts ; https://esbeshop.ru/elektricheskij-privod-povorotnyj-3-tochechnyj-esbe-95-220v-15nm-30-180-60sek-90-ko</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Аврора» (avrora-arm.ru)</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Москва, ул. Зеленодольская, д. 3</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>+7 (495) 956-62-18</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>sales@avrora-arm.ru</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>https://avrora-arm.ru</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>1.3/163</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">В каталоге прямоходные приводы REGADA серии Standard (ST 0, ST 0.1, ST 2, MTR), то есть поставка оригинала ST0 490.0-00TQV/00. Статус официального дистрибьютора на сайте не заявлен. Оригинал — импорт </t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>нет (импорт REGADA, Словакия)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>https://avrora-arm.ru/contact-us/ ; https://avrora-arm.ru/produkcziya/elektroprivodyi/regada/pryamoxodnyie/standard/elektroprivod-pryamoxodnyij-st-2-regada.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ПО БЗТпА» (Брянский завод трубопроводной арматуры, bztpa.ru)</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>новый (исследование 27.10)</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Москва (юр. адрес); склад готовой продукции — Брянск, Московский пр-д, 29</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>+7 (4832) 32-20-22</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>info@bztpa.ru</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>https://bztpa.ru</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
           <t>1.3/150</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K30" s="4" t="inlineStr">
         <is>
           <t>В номенклатуре «Затвор 32нж910р» DN150–2200, в том числе DN1000. Из материалов указаны 10Х18Н9Т и 08Х17Н13М2 (для морской воды предпочтительнее 08Х17Н13М2). Электропривод (по ТЗ ГЗ-В 600) и КОФ — отде</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
         <is>
           <t>не найдено</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>https://bztpa.ru/contact ; https://bztpa.ru/zatvory-stalnye</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M27"/>
+  <autoFilter ref="A1:M30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Компания</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Тип</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Город</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Телефон (не подтверждён в 2 источниках)</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Сайт</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Позиций</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Какие позиции</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Что именно / почему не подтверждено</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Источники</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Березовский завод трубопроводной арматуры» (БЗТА)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>г. Березовский (Свердловская обл.)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>+7 (343) 301-34-00</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>sale@bzta.ru</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>https://bzta.ru</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>113</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.1/21, 1.2/1, 1.2/2, 1.2/3, 1.2/4, 1.2/5, 1.3/106, 1.3/107, 1.3/108, 1.3/109, 1.3/110, 1.3/111, 1.3/112, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.3/127, 1.3/128, 1.3/129, 1.3/130, 1.3/131, 1.3/132, 1.3/133, 1.3/134, 1.3/13</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Краны стальные под приварку и фланцевые Ду25–1200 Ру6–40 (стальные позиции Ду≥25); латунные «Американка» 11б27п1 Ду15–50 — исполнение «американка», а не прямой муфтовый: уточнить соответствие ТЗ. Ду15</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>https://bzta.ru/kontakty/ ; https://2gis.ru/ekaterinburg/firm/70000001045757729</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Снабарматура» (официальный дилер LD в Хабаровске)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>г. Хабаровск, ул. Джамбула, 62, оф. 3</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>+7 (4212) 57-57-99</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>snabarmatura27@gmail.com</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>https://snabarmatura.ru</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.1/21, 1.2/1, 1.2/2, 1.2/3, 1.2/4, 1.2/5, 1.3/106, 1.3/107, 1.3/108, 1.3/109, 1.3/110, 1.3/111, 1.3/112, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.3/127, 1.3/128, 1.3/129, 1.3/130, 1.3/131, 1.3/132, 1.3/13</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Склад на ДВ, около 239 позиций LD: КШЦФ/КШЦП/КШЦМ/разборные, Ду15–1000, Ру16/25/40, ст.20/09Г2С. Закрывает «LD КШРФ/КШЦФ» в точном бренде и стальные 11с67п/11с22п как эквиваленты LD; муфтовый Ду25 Ру4</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>https://snabarmatura.ru/about/ ; https://2gis.ru/khabarovsk/firm/4926340373419954 ; https://saby.ru/profile/2722106708</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ТД «Центр Снабжения» (cs27.ru)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>г. Хабаровск, ул. Промышленная, 7 (+ Владивосток, Снеговая 18а; Чита, Благовещенск, Находка, Южно-Сахалинск)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>+7 (4212) 37-22-33</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>372233@cs27.ru</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>https://cs27.ru</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>95</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>1.1/20, 1.1/21, 1.2/1, 1.2/2, 1.2/3, 1.2/4, 1.2/5, 1.3/106, 1.3/107, 1.3/108, 1.3/109, 1.3/110, 1.3/111, 1.3/112, 1.3/113, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.3/120, 1.3/121, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.3/127, 1.3/128, 1.3/129, 1.3/130, 1.3/131, 1.3/132, 1.3/13</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Оптовый склад на ДВ: краны Маршал 11с67п под приварку, фланцевые GAS PRO, нестандартные. Закрывает стальные приварные Ру25 и фланцевые Ру16/25 как эквиваленты Маршал (завод Маршал уже в known). Латунь</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>https://cs27.ru/contacts/ ; https://2gis.ru/khabarovsk/firm/4926340373606119 ; https://2gis.ru/vladivostok/firm/70000001006939486</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>«Инженер Теплотехник» (tt41.ru)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>г. Петропавловск-Камчатский, пр-т Циолковского, 6/1</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>+7 (4152) 307-100</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>teplomag@tt41.ru</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>https://tt41.ru</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>1.1/21, 1.2/3, 1.2/4, 1.2/5, 1.3/106, 1.3/107, 1.3/108, 1.3/109, 1.3/110, 1.3/111, 1.3/112, 1.3/122, 1.3/123, 1.3/124, 1.3/125, 1.3/126, 1.3/127, 1.3/128, 1.3/129, 1.3/130, 1.3/131, 1.3/132, 1.3/133, 1.3/134, 1.3/136, 1.3/137, 1.3/138, 1.3/139, 1.3/140, 1.3/141, 1.3/142, 1.3/143, 1.3/144, 1.3/145, 1</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Местный склад в Петропавловске-Камчатском: стальные фланцевые краны MARSHAL Ду15–300 (наличие небольшое), латунь VALTEC (импорт — под ПП 1875 не годится). Подходит для срочной допоставки и отгрузки «д</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>https://tt41.ru/contacts/ ; https://2gis.ru/p_kamchatskiy/firm/70000001037871393</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>VALFEX (ООО «Теплосеть-Импорт», арматурный завод г. Вязники; группа ООО «ВАЛФ-РУС»)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>г. Владимир / г. Вязники (Владимирская обл.)</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>+7 (4922) 40-05-35</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>info@valfex.ru</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>https://valfex.ru</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>1.1/14, 1.1/15, 1.1/16, 1.1/17, 1.1/18, 1.1/19, 1.3/101, 1.3/102, 1.3/103, 1.3/104, 1.3/105, 1.5/4, 1.5/5, 1.5/6, 1.5/7, 1.5/8, 1.6/51, 1.6/52, 1.6/53, 1.6/54, 1.6/55, 1.6/56</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>Российский производитель латунных шаровых кранов (серии STANDART/PREMIUM, 11Б27фт1М, ГОСТ 15527) — позиции 11б27п1; диапазон Ду40–50 уточнить.</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>https://valfex.ru/contacts/ ; https://2gis.ru/vladimir/firm/8304040093945606 ; https://saby.ru/profile/3328015934</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>«Град Сталь» (металлобаза)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>г. Хабаровск, ул. Ангарская, 4</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>+7 (4212) 543-145</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>gradstal@mail.ru</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>https://gradstal.ru</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>1.2/1, 1.2/2, 1.3/114, 1.3/115, 1.3/116, 1.3/117, 1.3/118, 1.3/119, 1.5/13, 1.5/14, 1.5/15, 1.5/16, 1.5/17, 1.6/68, 1.6/69, 1.6/70, 1.7/2, 1.7/3, 1.7/4</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>Склад в Хабаровске: краны ALSO КШ.П под приварку Ду25–100 (PN40 Ду25–50, PN25 Ду65–100) — позиции 11с67п под приварку Ру25 Ду25–100. Сам ALSO уже в known, но склад на ДВ с ценой.</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>https://gradstal.ru/contacts/ ; https://2gis.ru/khabarovsk/firm/4926340373422449</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Newkey (ООО, СПб; «БАЗ Newkey»)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>+7 (812) 449-00-76</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>zakaz@newkey.ru</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>newkey.ru</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>1.3/135</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>Есть нерж. муфтовые AISI316 PN64, но на странице «О нас»: «работа напрямую с производителями и поставщиками», 1000 м² производственно-складской площади — признаков собственного производства кранов нет</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Сварат»</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>завод</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Чебоксары, пр-д Машиностроителей, 1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>+7 (902) 240-21-21</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>m.svarat@yandex.ru</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>1.4/1</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Заявлено изготовление самоомывающихся рыбозащитных устройств РЗУ/РОП разных типоразмеров (РОП-50/175/300/500; РОП-200 под насос от 250 м³/ч, сталь 20, переход на Ду200, ячейка 4 мм — запрашивать как с</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>https://productcenter.ru/producers/38903/ooo-svarat ; https://promvest.info/ru/goods/ryibozaschitnoe-ustroystvo-rzu-rop-samoomyivayuscheesya/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ТД «КамчатТехПром» (ktp41.ru)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>дистрибьютор</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>г. Петропавловск-Камчатский</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>+7 (4152) 258-227</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>ktp69@yandex.ru</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>https://ktp41.ru</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>Местный поставщик металлопроката и арматуры: разделы «краны шаровые фланцевые / муфтовые / под приварку», бренды не указаны. Можно запросить как логистического партнёра в Петропавловске; покрытие пози</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>https://ktp41.ru/kontakty</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2836,7 +3572,7 @@
       </c>
       <c r="U2" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V2" s="4" t="inlineStr">
@@ -2940,7 +3676,7 @@
       </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V3" s="4" t="inlineStr">
@@ -3040,7 +3776,7 @@
       </c>
       <c r="U4" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V4" s="4" t="inlineStr">
@@ -3144,7 +3880,7 @@
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
@@ -3244,7 +3980,7 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
@@ -3348,7 +4084,7 @@
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V7" s="4" t="inlineStr">
@@ -3456,7 +4192,7 @@
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
@@ -3562,7 +4298,7 @@
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
@@ -3670,7 +4406,7 @@
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
@@ -3774,7 +4510,7 @@
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
@@ -3878,7 +4614,7 @@
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
@@ -3982,7 +4718,7 @@
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V13" s="4" t="inlineStr">
@@ -4091,7 +4827,7 @@
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V14" s="4" t="inlineStr">
@@ -4195,7 +4931,7 @@
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V15" s="4" t="inlineStr">
@@ -4299,7 +5035,7 @@
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V16" s="4" t="inlineStr">
@@ -4399,7 +5135,7 @@
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V17" s="4" t="inlineStr">
@@ -4503,7 +5239,7 @@
       </c>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V18" s="4" t="inlineStr">
@@ -4607,7 +5343,7 @@
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V19" s="4" t="inlineStr">
@@ -4715,7 +5451,7 @@
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V20" s="4" t="inlineStr">
@@ -4823,7 +5559,7 @@
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr">
@@ -4931,7 +5667,7 @@
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr">
@@ -5035,7 +5771,7 @@
       </c>
       <c r="U23" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr">
@@ -5139,7 +5875,7 @@
       </c>
       <c r="U24" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V24" s="4" t="inlineStr">
@@ -5243,7 +5979,7 @@
       </c>
       <c r="U25" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V25" s="4" t="inlineStr">
@@ -5347,7 +6083,7 @@
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr">
@@ -5450,7 +6186,7 @@
       </c>
       <c r="U27" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V27" s="4" t="inlineStr">
@@ -5546,7 +6282,7 @@
       </c>
       <c r="U28" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V28" s="4" t="inlineStr">
@@ -5650,7 +6386,7 @@
       </c>
       <c r="U29" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V29" s="4" t="inlineStr">
@@ -5753,7 +6489,7 @@
       </c>
       <c r="U30" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V30" s="4" t="inlineStr">
@@ -5857,7 +6593,7 @@
       </c>
       <c r="U31" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V31" s="4" t="inlineStr">
@@ -5961,7 +6697,7 @@
       </c>
       <c r="U32" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V32" s="4" t="inlineStr">
@@ -6065,7 +6801,7 @@
       </c>
       <c r="U33" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V33" s="4" t="inlineStr">
@@ -6169,7 +6905,7 @@
       </c>
       <c r="U34" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V34" s="4" t="inlineStr">
@@ -6273,7 +7009,7 @@
       </c>
       <c r="U35" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V35" s="4" t="inlineStr">
@@ -6377,7 +7113,7 @@
       </c>
       <c r="U36" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V36" s="4" t="inlineStr">
@@ -6481,7 +7217,7 @@
       </c>
       <c r="U37" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V37" s="4" t="inlineStr">
@@ -6585,7 +7321,7 @@
       </c>
       <c r="U38" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V38" s="4" t="inlineStr">
@@ -6689,7 +7425,7 @@
       </c>
       <c r="U39" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V39" s="4" t="inlineStr">
@@ -6793,7 +7529,7 @@
       </c>
       <c r="U40" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V40" s="4" t="inlineStr">
@@ -6902,7 +7638,7 @@
       </c>
       <c r="U41" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V41" s="4" t="inlineStr">
@@ -7011,7 +7747,7 @@
       </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V42" s="4" t="inlineStr">
@@ -7120,7 +7856,7 @@
       </c>
       <c r="U43" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V43" s="4" t="inlineStr">
@@ -7229,7 +7965,7 @@
       </c>
       <c r="U44" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V44" s="4" t="inlineStr">
@@ -7329,7 +8065,7 @@
       </c>
       <c r="U45" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V45" s="4" t="inlineStr">
@@ -7429,7 +8165,7 @@
       </c>
       <c r="U46" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V46" s="4" t="inlineStr">
@@ -7529,7 +8265,7 @@
       </c>
       <c r="U47" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V47" s="4" t="inlineStr">
@@ -7629,7 +8365,7 @@
       </c>
       <c r="U48" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V48" s="4" t="inlineStr">
@@ -7829,7 +8565,7 @@
       </c>
       <c r="U50" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V50" s="4" t="inlineStr">
@@ -7933,7 +8669,7 @@
       </c>
       <c r="U51" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V51" s="4" t="inlineStr">
@@ -8037,7 +8773,7 @@
       </c>
       <c r="U52" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V52" s="4" t="inlineStr">
@@ -8141,7 +8877,7 @@
       </c>
       <c r="U53" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V53" s="4" t="inlineStr">
@@ -8241,7 +8977,7 @@
       </c>
       <c r="U54" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V54" s="4" t="inlineStr">
@@ -8341,7 +9077,7 @@
       </c>
       <c r="U55" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V55" s="4" t="inlineStr">
@@ -8441,7 +9177,7 @@
       </c>
       <c r="U56" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V56" s="4" t="inlineStr">
@@ -8541,7 +9277,7 @@
       </c>
       <c r="U57" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V57" s="4" t="inlineStr">
@@ -8641,7 +9377,7 @@
       </c>
       <c r="U58" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V58" s="4" t="inlineStr">
@@ -8741,7 +9477,7 @@
       </c>
       <c r="U59" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V59" s="4" t="inlineStr">
@@ -9049,7 +9785,7 @@
       </c>
       <c r="U62" s="4" t="inlineStr">
         <is>
-          <t>ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V62" s="4" t="inlineStr">
@@ -9145,7 +9881,7 @@
       </c>
       <c r="U63" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V63" s="4" t="inlineStr">
@@ -9249,7 +9985,7 @@
       </c>
       <c r="U64" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V64" s="4" t="inlineStr">
@@ -9357,7 +10093,7 @@
       </c>
       <c r="U65" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V65" s="4" t="inlineStr">
@@ -9457,7 +10193,7 @@
       </c>
       <c r="U66" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V66" s="4" t="inlineStr">
@@ -9561,7 +10297,7 @@
       </c>
       <c r="U67" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V67" s="4" t="inlineStr">
@@ -9665,7 +10401,7 @@
       </c>
       <c r="U68" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V68" s="4" t="inlineStr">
@@ -9773,7 +10509,7 @@
       </c>
       <c r="U69" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V69" s="4" t="inlineStr">
@@ -9881,7 +10617,7 @@
       </c>
       <c r="U70" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V70" s="4" t="inlineStr">
@@ -9989,7 +10725,7 @@
       </c>
       <c r="U71" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V71" s="4" t="inlineStr">
@@ -10092,7 +10828,7 @@
       </c>
       <c r="U72" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V72" s="4" t="inlineStr">
@@ -10188,7 +10924,7 @@
       </c>
       <c r="U73" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V73" s="4" t="inlineStr">
@@ -10292,7 +11028,7 @@
       </c>
       <c r="U74" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V74" s="4" t="inlineStr">
@@ -10395,7 +11131,7 @@
       </c>
       <c r="U75" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V75" s="4" t="inlineStr">
@@ -10499,7 +11235,7 @@
       </c>
       <c r="U76" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V76" s="4" t="inlineStr">
@@ -10603,7 +11339,7 @@
       </c>
       <c r="U77" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V77" s="4" t="inlineStr">
@@ -10707,7 +11443,7 @@
       </c>
       <c r="U78" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V78" s="4" t="inlineStr">
@@ -10815,7 +11551,7 @@
       </c>
       <c r="U79" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V79" s="4" t="inlineStr">
@@ -10923,7 +11659,7 @@
       </c>
       <c r="U80" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V80" s="4" t="inlineStr">
@@ -11031,7 +11767,7 @@
       </c>
       <c r="U81" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V81" s="4" t="inlineStr">
@@ -11139,7 +11875,7 @@
       </c>
       <c r="U82" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V82" s="4" t="inlineStr">
@@ -11247,7 +11983,7 @@
       </c>
       <c r="U83" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V83" s="4" t="inlineStr">
@@ -11355,7 +12091,7 @@
       </c>
       <c r="U84" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «ТЕМПЕР» +7 (3522) 22-88-88; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «ГАЛЛОП» +7 (383) 355-10-00</t>
         </is>
       </c>
       <c r="V84" s="4" t="inlineStr">
@@ -11463,7 +12199,7 @@
       </c>
       <c r="U85" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V85" s="4" t="inlineStr">
@@ -11571,7 +12307,7 @@
       </c>
       <c r="U86" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V86" s="4" t="inlineStr">
@@ -11679,7 +12415,7 @@
       </c>
       <c r="U87" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V87" s="4" t="inlineStr">
@@ -11787,7 +12523,7 @@
       </c>
       <c r="U88" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V88" s="4" t="inlineStr">
@@ -11895,7 +12631,7 @@
       </c>
       <c r="U89" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V89" s="4" t="inlineStr">
@@ -12003,7 +12739,7 @@
       </c>
       <c r="U90" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V90" s="4" t="inlineStr">
@@ -12113,7 +12849,7 @@
       </c>
       <c r="U91" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V91" s="4" t="inlineStr">
@@ -12223,7 +12959,7 @@
       </c>
       <c r="U92" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V92" s="4" t="inlineStr">
@@ -12333,7 +13069,7 @@
       </c>
       <c r="U93" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V93" s="4" t="inlineStr">
@@ -12443,7 +13179,7 @@
       </c>
       <c r="U94" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V94" s="4" t="inlineStr">
@@ -12553,7 +13289,7 @@
       </c>
       <c r="U95" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V95" s="4" t="inlineStr">
@@ -12661,7 +13397,7 @@
       </c>
       <c r="U96" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V96" s="4" t="inlineStr">
@@ -12769,7 +13505,7 @@
       </c>
       <c r="U97" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V97" s="4" t="inlineStr">
@@ -12877,7 +13613,7 @@
       </c>
       <c r="U98" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V98" s="4" t="inlineStr">
@@ -12988,7 +13724,7 @@
       </c>
       <c r="U99" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V99" s="4" t="inlineStr">
@@ -13099,7 +13835,7 @@
       </c>
       <c r="U100" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V100" s="4" t="inlineStr">
@@ -13210,7 +13946,7 @@
       </c>
       <c r="U101" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V101" s="4" t="inlineStr">
@@ -13321,7 +14057,7 @@
       </c>
       <c r="U102" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V102" s="4" t="inlineStr">
@@ -13432,7 +14168,7 @@
       </c>
       <c r="U103" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V103" s="4" t="inlineStr">
@@ -13543,7 +14279,7 @@
       </c>
       <c r="U104" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V104" s="4" t="inlineStr">
@@ -13658,7 +14394,7 @@
       </c>
       <c r="U105" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V105" s="4" t="inlineStr">
@@ -13773,7 +14509,7 @@
       </c>
       <c r="U106" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V106" s="4" t="inlineStr">
@@ -13888,7 +14624,7 @@
       </c>
       <c r="U107" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V107" s="4" t="inlineStr">
@@ -14003,7 +14739,7 @@
       </c>
       <c r="U108" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V108" s="4" t="inlineStr">
@@ -14110,7 +14846,7 @@
       </c>
       <c r="U109" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V109" s="4" t="inlineStr">
@@ -14210,7 +14946,7 @@
       </c>
       <c r="U110" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V110" s="4" t="inlineStr">
@@ -14313,7 +15049,7 @@
       </c>
       <c r="U111" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V111" s="4" t="inlineStr">
@@ -14416,7 +15152,7 @@
       </c>
       <c r="U112" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V112" s="4" t="inlineStr">
@@ -14519,7 +15255,7 @@
       </c>
       <c r="U113" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V113" s="4" t="inlineStr">
@@ -14622,7 +15358,7 @@
       </c>
       <c r="U114" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V114" s="4" t="inlineStr">
@@ -14725,7 +15461,7 @@
       </c>
       <c r="U115" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V115" s="4" t="inlineStr">
@@ -14828,7 +15564,7 @@
       </c>
       <c r="U116" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V116" s="4" t="inlineStr">
@@ -14936,7 +15672,7 @@
       </c>
       <c r="U117" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V117" s="4" t="inlineStr">
@@ -15044,7 +15780,7 @@
       </c>
       <c r="U118" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V118" s="4" t="inlineStr">
@@ -15152,7 +15888,7 @@
       </c>
       <c r="U119" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V119" s="4" t="inlineStr">
@@ -15252,7 +15988,7 @@
       </c>
       <c r="U120" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ЛЗТА «Маршал» 8 (800) 301-20-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V120" s="4" t="inlineStr">
@@ -15352,7 +16088,7 @@
       </c>
       <c r="U121" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ЛЗТА «Маршал» 8 (800) 301-20-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V121" s="4" t="inlineStr">
@@ -15452,7 +16188,7 @@
       </c>
       <c r="U122" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ЛЗТА «Маршал» 8 (800) 301-20-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V122" s="4" t="inlineStr">
@@ -15552,7 +16288,7 @@
       </c>
       <c r="U123" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V123" s="4" t="inlineStr">
@@ -15652,7 +16388,7 @@
       </c>
       <c r="U124" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V124" s="4" t="inlineStr">
@@ -15752,7 +16488,7 @@
       </c>
       <c r="U125" s="4" t="inlineStr">
         <is>
-          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50</t>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд +7 (351) 730-47-47; ООО «АЛСО» 8-800-444-74-74; ООО «Краны Балашихи» +7 (495) 275-58-88 (на сайте: +7 (495) 27-55-888); ЛЗТА «Маршал» 8 (800) 301-20-50; ООО «ТЕМПЕР» +7 (3522) 22-88-88; РОБЕН +7 (495) 228-11-50; ООО «Угрешский завод трубопроводной арматуры» +7 (495) 120-57-89; ООО «Уральский завод трубопроводной арматуры» +7 (351) 222-11-40</t>
         </is>
       </c>
       <c r="V125" s="4" t="inlineStr">
@@ -15768,7 +16504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16531,7 +17267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18059,7 +18795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18315,7 +19051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/KAMCHATKA_OPEN_ZAPROS_2710.xlsx
+++ b/KAMCHATKA_OPEN_ZAPROS_2710.xlsx
@@ -9,20 +9,21 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итог" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кому запросить" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кандидаты без проверки" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Краны" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Затворы" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Клапаны" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задвижки" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приводы и прочее" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Письма" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Кандидаты без проверки" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Краны" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Затворы" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Клапаны" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Задвижки" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Приводы и прочее" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Кому запросить'!$A$1:$M$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Краны'!$A$1:$V$125</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Затворы'!$A$1:$V$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Клапаны'!$A$1:$V$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Задвижки'!$A$1:$V$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Приводы и прочее'!$A$1:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Краны'!$A$1:$V$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Затворы'!$A$1:$V$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Клапаны'!$A$1:$V$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Задвижки'!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Приводы и прочее'!$A$1:$V$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2792,6 +2793,1829 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="120" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="48" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Кому</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Тема</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Текст письма (позиции — во вложении: лист группы, отфильтровать по «Табл./№ ТЗ»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="409" customHeight="1">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ЧелябинскСпецГражданСтрой» / ЛД Прайд (Группа компаний «ЛД», ТМ LD, LD Pride); продажи — ООО «ТД «ЛД»</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>office@chsgs.ru</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 122 поз.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/14 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 35 шт
+1.1/15 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 35 шт
+1.1/16 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 20 шт
+1.1/17 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 25 шт
+1.1/18 — Кран шаровой 11б27п1 Ду 40 Ру 16 — 8 шт
+1.1/19 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 8 шт
+1.1/20 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.1/21 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.2/1 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 2 шт
+1.2/2 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.2/3 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 18 шт
+1.2/4 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.2/5 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.3/101 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 110 шт
+1.3/102 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 57 шт
+1.3/103 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 29 шт
+1.3/104 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 47 шт
+1.3/105 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 24 шт
+1.3/106 — Кран шаровой фланцевый 11с22п Ду 50 Ру 16 — 7 шт
+1.3/107 — Кран шаровой фланцевый 11с22п Ду 80 Ру 16 — 8 шт
+1.3/108 — Кран шаровой фланцевый 11с22п Ду 100 Ру 16 — 8 шт
+1.3/109 — Кран шаровой 11С67П Ду 100 Ру 16 — 2 шт
+1.3/110 — Кран шаровой 11С67П Ду 150 Ру 16 — 2 шт
+1.3/111 — Кран шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.3/112 — Кран шаровой 11С67П Ду 80 Ру 16 — 2 шт
+1.3/113 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 62 шт
+1.3/114 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 48 шт
+1.3/115 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 40 шт
+1.3/116 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 38 шт
+1.3/117 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 44 шт
+1.3/118 — Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку — 26 шт
+1.3/119 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 24 шт
+1.3/120 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 22 шт
+1.3/121 — Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку — 10 шт
+1.3/122 — Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 3 шт
+1.3/123 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/124 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.3/125 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/126 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.3/127 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 91 шт
+1.3/128 — Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 10 шт
+1.3/129 — Кран шаровой 11с67п Ду 150 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 59 шт
+1.3/130 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 45 шт
+1.3/131 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 8 шт
+1.3/132 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 80 шт
+1.3/133 — Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.3/134 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 92 шт
+1.3/136 — Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ — 14 шт
+1.3/137 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 29 шт
+1.3/138 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ — 6 шт
+1.3/139 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 31 шт
+1.3/140 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 8 шт
+1.3/141 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ — 8 шт
+1.3/142 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 8 шт
+1.3/143 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 112 шт
+1.3/144 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ — 6 шт
+1.3/145 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ — 58 шт
+1.3/146 — Кран шаровый химический КШХ Ду 50 Ру 16 — 2 шт
+1.3/147 — Кран шаровый химический КШХ Ду 80 Ру 16 — 4 шт
+1.3/149 — Кран шаровый цельносварной неполнопроходной 11с67п Ду 250/200 Ру 16 с КОФ — 2 шт
+1.5/4 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 28 шт
+1.5/5 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 16 шт
+1.5/6 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 16 шт
+1.5/7 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 6 шт
+1.5/8 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 6 шт
+1.5/9 — Кран шаровой 11с22п Ду 50 Ру 16 — 4 шт
+1.5/10 — Кран шаровой 11с22п Ду 80 Ру 16 — 4 шт
+1.5/11 — Кран шаровой 11с22п Ду 100 Ру 16 — 2 шт
+1.5/12 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 25 шт
+1.5/13 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 32 шт
+1.5/14 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 15 шт
+1.5/15 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 26 шт
+1.5/16 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 9 шт
+1.5/17 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.5/18 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.6/51 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 47 шт
+1.6/52 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 63 шт
+1.6/53 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 40 шт
+1.6/54 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 77 шт
+1.6/55 — Кран шаровой 11б27п1 Ду 40 Ру 16 — 2 шт
+1.6/56 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 6 шт
+1.6/57 — Кран шаровой 11с22п Ду 32 Ру 16 — 55 шт
+1.6/58 — Кран шаровой 11с22п Ду 50 Ру 16 — 35 шт
+1.6/59 — Кран шаровой 11с22п Ду 80 Ру 16 — 24 шт
+1.6/60 — Кран шаровой 11с22п Ду 100 Ру 16 — 27 шт
+1.6/61 — Кран шаровой 11с22п Ду 150 Ру 16 — 13 шт
+1.6/62 — Кран шаровой 11с22п Ду 200 Ру 16 — 3 шт
+1.6/63 — Кран запорный шаровой 11С67П Ду 100 Ру 16 — 25 шт
+1.6/64 — Кран запорный шаровой 11С67П Ду 150 Ру 16 — 9 шт
+1.6/65 — Кран запорный шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.6/66 — Кран запорный шаровой 11С67П Ду 50 Ру 16 — 25 шт
+1.6/67 — Кран запорный шаровой 11С67П Ду 80 Ру 16 — 22 шт
+1.6/68 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 36 шт
+1.6/69 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 6 шт
+1.6/70 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.6/71 — Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/72 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/73 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.6/74 — Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/75 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/76 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/77 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 4 шт
+1.6/78 — Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/79 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/80 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 3 шт
+1.6/81 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.6/82 — Кран шаровой TEMPER 28020025 муфтовый, Ду 25, Ру 40 — 2 шт
+1.6/83 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 3 шт
+1.6/84 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 1 шт
+1.6/85 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 2 шт
+1.6/86 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 6 шт
+1.6/87 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 5 шт
+1.6/88 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ — 6 шт
+1.7/2 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 12 шт
+1.7/3 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 12 шт
+1.7/4 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.8/2 — Кран шаровой 10нж45фт 2ЦФ Ду 20 Ру 16 — 2 шт
+1.8/3 — Кран шаровой 10нж45фт 2ЦФ Ду 25 Ру 16 — 2 шт
+1.8/4 — Кран шаровой 10нж45фт 2ЦФ Ду 32 Ру 16 — 2 шт
+1.8/5 — Кран шаровой 11с22п Ду 80 Ру 16 — 2 шт
+1.8/6 — Кран шаровой 11с22п Ду 100 Ру 16 — 1 шт
+1.8/7 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="409" customHeight="1">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ТЕМПЕР» (завод TEMPER)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>temper@temper.ru</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 117 поз.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/14 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 35 шт
+1.1/15 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 35 шт
+1.1/16 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 20 шт
+1.1/17 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 25 шт
+1.1/18 — Кран шаровой 11б27п1 Ду 40 Ру 16 — 8 шт
+1.1/19 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 8 шт
+1.1/20 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.1/21 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.2/1 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 2 шт
+1.2/2 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.2/3 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 18 шт
+1.2/4 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.2/5 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.3/101 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 110 шт
+1.3/102 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 57 шт
+1.3/103 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 29 шт
+1.3/104 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 47 шт
+1.3/105 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 24 шт
+1.3/106 — Кран шаровой фланцевый 11с22п Ду 50 Ру 16 — 7 шт
+1.3/107 — Кран шаровой фланцевый 11с22п Ду 80 Ру 16 — 8 шт
+1.3/108 — Кран шаровой фланцевый 11с22п Ду 100 Ру 16 — 8 шт
+1.3/109 — Кран шаровой 11С67П Ду 100 Ру 16 — 2 шт
+1.3/110 — Кран шаровой 11С67П Ду 150 Ру 16 — 2 шт
+1.3/111 — Кран шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.3/112 — Кран шаровой 11С67П Ду 80 Ру 16 — 2 шт
+1.3/113 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 62 шт
+1.3/114 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 48 шт
+1.3/115 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 40 шт
+1.3/116 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 38 шт
+1.3/117 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 44 шт
+1.3/118 — Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку — 26 шт
+1.3/119 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 24 шт
+1.3/120 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 22 шт
+1.3/121 — Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку — 10 шт
+1.3/122 — Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 3 шт
+1.3/123 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/124 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.3/125 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/126 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.3/127 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 91 шт
+1.3/128 — Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 10 шт
+1.3/129 — Кран шаровой 11с67п Ду 150 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 59 шт
+1.3/130 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 45 шт
+1.3/131 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 8 шт
+1.3/132 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 80 шт
+1.3/133 — Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.3/134 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 92 шт
+1.3/136 — Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ — 14 шт
+1.3/137 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 29 шт
+1.3/138 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ — 6 шт
+1.3/139 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 31 шт
+1.3/140 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 8 шт
+1.3/141 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ — 8 шт
+1.3/142 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 8 шт
+1.3/143 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 112 шт
+1.3/144 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ — 6 шт
+1.3/145 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ — 58 шт
+1.3/148 — Кран шаровый разборный полнопроходной 11с67п Ду 250 Ру 16 с КОФ — 6 шт
+1.5/4 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 28 шт
+1.5/5 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 16 шт
+1.5/6 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 16 шт
+1.5/7 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 6 шт
+1.5/8 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 6 шт
+1.5/9 — Кран шаровой 11с22п Ду 50 Ру 16 — 4 шт
+1.5/10 — Кран шаровой 11с22п Ду 80 Ру 16 — 4 шт
+1.5/11 — Кран шаровой 11с22п Ду 100 Ру 16 — 2 шт
+1.5/12 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 25 шт
+1.5/13 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 32 шт
+1.5/14 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 15 шт
+1.5/15 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 26 шт
+1.5/16 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 9 шт
+1.5/17 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.5/18 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.6/51 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 47 шт
+1.6/52 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 63 шт
+1.6/53 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 40 шт
+1.6/54 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 77 шт
+1.6/55 — Кран шаровой 11б27п1 Ду 40 Ру 16 — 2 шт
+1.6/56 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 6 шт
+1.6/57 — Кран шаровой 11с22п Ду 32 Ру 16 — 55 шт
+1.6/58 — Кран шаровой 11с22п Ду 50 Ру 16 — 35 шт
+1.6/59 — Кран шаровой 11с22п Ду 80 Ру 16 — 24 шт
+1.6/60 — Кран шаровой 11с22п Ду 100 Ру 16 — 27 шт
+1.6/61 — Кран шаровой 11с22п Ду 150 Ру 16 — 13 шт
+1.6/62 — Кран шаровой 11с22п Ду 200 Ру 16 — 3 шт
+1.6/63 — Кран запорный шаровой 11С67П Ду 100 Ру 16 — 25 шт
+1.6/64 — Кран запорный шаровой 11С67П Ду 150 Ру 16 — 9 шт
+1.6/65 — Кран запорный шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.6/66 — Кран запорный шаровой 11С67П Ду 50 Ру 16 — 25 шт
+1.6/67 — Кран запорный шаровой 11С67П Ду 80 Ру 16 — 22 шт
+1.6/68 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 36 шт
+1.6/69 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 6 шт
+1.6/70 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.6/71 — Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/72 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/73 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.6/74 — Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/75 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/76 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/77 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 4 шт
+1.6/78 — Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/79 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/80 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 3 шт
+1.6/81 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.6/82 — Кран шаровой TEMPER 28020025 муфтовый, Ду 25, Ру 40 — 2 шт
+1.6/83 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 3 шт
+1.6/84 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 1 шт
+1.6/85 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 2 шт
+1.6/86 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 6 шт
+1.6/87 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 5 шт
+1.6/88 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ — 6 шт
+1.7/2 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 12 шт
+1.7/3 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 12 шт
+1.7/4 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.8/5 — Кран шаровой 11с22п Ду 80 Ру 16 — 2 шт
+1.8/6 — Кран шаровой 11с22п Ду 100 Ру 16 — 1 шт
+1.8/7 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="409" customHeight="1">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Угрешский завод трубопроводной арматуры» (УЗТПА, ТМ «УГРЕША», серии AQUARIUS/NEON)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>info@uztpa.ru</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 117 поз.</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/14 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 35 шт
+1.1/15 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 35 шт
+1.1/16 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 20 шт
+1.1/17 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 25 шт
+1.1/18 — Кран шаровой 11б27п1 Ду 40 Ру 16 — 8 шт
+1.1/19 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 8 шт
+1.1/20 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.1/21 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.2/1 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 2 шт
+1.2/2 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.2/3 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 18 шт
+1.2/4 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.2/5 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.3/101 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 110 шт
+1.3/102 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 57 шт
+1.3/103 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 29 шт
+1.3/104 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 47 шт
+1.3/105 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 24 шт
+1.3/106 — Кран шаровой фланцевый 11с22п Ду 50 Ру 16 — 7 шт
+1.3/107 — Кран шаровой фланцевый 11с22п Ду 80 Ру 16 — 8 шт
+1.3/108 — Кран шаровой фланцевый 11с22п Ду 100 Ру 16 — 8 шт
+1.3/109 — Кран шаровой 11С67П Ду 100 Ру 16 — 2 шт
+1.3/110 — Кран шаровой 11С67П Ду 150 Ру 16 — 2 шт
+1.3/111 — Кран шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.3/112 — Кран шаровой 11С67П Ду 80 Ру 16 — 2 шт
+1.3/113 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 62 шт
+1.3/114 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 48 шт
+1.3/115 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 40 шт
+1.3/116 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 38 шт
+1.3/117 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 44 шт
+1.3/118 — Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку — 26 шт
+1.3/119 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 24 шт
+1.3/120 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 22 шт
+1.3/121 — Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку — 10 шт
+1.3/122 — Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 3 шт
+1.3/123 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/124 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.3/125 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/126 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.3/127 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 91 шт
+1.3/128 — Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 10 шт
+1.3/129 — Кран шаровой 11с67п Ду 150 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 59 шт
+1.3/130 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 45 шт
+1.3/131 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 8 шт
+1.3/132 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 80 шт
+1.3/133 — Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.3/134 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 92 шт
+1.3/136 — Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ — 14 шт
+1.3/137 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 29 шт
+1.3/138 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ — 6 шт
+1.3/139 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 31 шт
+1.3/140 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 8 шт
+1.3/141 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ — 8 шт
+1.3/142 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 8 шт
+1.3/143 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 112 шт
+1.3/144 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ — 6 шт
+1.3/145 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ — 58 шт
+1.3/148 — Кран шаровый разборный полнопроходной 11с67п Ду 250 Ру 16 с КОФ — 6 шт
+1.3/149 — Кран шаровый цельносварной неполнопроходной 11с67п Ду 250/200 Ру 16 с КОФ — 2 шт
+1.5/4 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 28 шт
+1.5/5 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 16 шт
+1.5/6 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 16 шт
+1.5/7 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 6 шт
+1.5/8 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 6 шт
+1.5/9 — Кран шаровой 11с22п Ду 50 Ру 16 — 4 шт
+1.5/10 — Кран шаровой 11с22п Ду 80 Ру 16 — 4 шт
+1.5/11 — Кран шаровой 11с22п Ду 100 Ру 16 — 2 шт
+1.5/12 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 25 шт
+1.5/13 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 32 шт
+1.5/14 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 15 шт
+1.5/15 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 26 шт
+1.5/16 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 9 шт
+1.5/17 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.5/18 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.6/51 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 47 шт
+1.6/52 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 63 шт
+1.6/53 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 40 шт
+1.6/54 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 77 шт
+1.6/55 — Кран шаровой 11б27п1 Ду 40 Ру 16 — 2 шт
+1.6/56 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 6 шт
+1.6/57 — Кран шаровой 11с22п Ду 32 Ру 16 — 55 шт
+1.6/58 — Кран шаровой 11с22п Ду 50 Ру 16 — 35 шт
+1.6/59 — Кран шаровой 11с22п Ду 80 Ру 16 — 24 шт
+1.6/60 — Кран шаровой 11с22п Ду 100 Ру 16 — 27 шт
+1.6/61 — Кран шаровой 11с22п Ду 150 Ру 16 — 13 шт
+1.6/62 — Кран шаровой 11с22п Ду 200 Ру 16 — 3 шт
+1.6/63 — Кран запорный шаровой 11С67П Ду 100 Ру 16 — 25 шт
+1.6/64 — Кран запорный шаровой 11С67П Ду 150 Ру 16 — 9 шт
+1.6/65 — Кран запорный шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.6/66 — Кран запорный шаровой 11С67П Ду 50 Ру 16 — 25 шт
+1.6/67 — Кран запорный шаровой 11С67П Ду 80 Ру 16 — 22 шт
+1.6/68 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 36 шт
+1.6/69 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 6 шт
+1.6/70 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.6/71 — Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/72 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/73 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.6/74 — Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/75 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/76 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/77 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 4 шт
+1.6/78 — Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/79 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/80 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 3 шт
+1.6/81 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.6/83 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 3 шт
+1.6/84 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 1 шт
+1.6/85 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 2 шт
+1.6/86 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 6 шт
+1.6/87 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 5 шт
+1.6/88 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ — 6 шт
+1.7/2 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 12 шт
+1.7/3 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 12 шт
+1.7/4 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.8/5 — Кран шаровой 11с22п Ду 80 Ру 16 — 2 шт
+1.8/6 — Кран шаровой 11с22п Ду 100 Ру 16 — 1 шт
+1.8/7 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="409" customHeight="1">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>ЛЗТА «Маршал» (Луганский завод трубопроводной арматуры); сайт и продажи — ООО «Арматура М», официальный дистрибьютор завода</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>info@lztamarshal.ru</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 101 поз.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/20 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.1/21 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.2/1 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 2 шт
+1.2/2 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.2/3 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 18 шт
+1.2/4 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.2/5 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.3/106 — Кран шаровой фланцевый 11с22п Ду 50 Ру 16 — 7 шт
+1.3/107 — Кран шаровой фланцевый 11с22п Ду 80 Ру 16 — 8 шт
+1.3/108 — Кран шаровой фланцевый 11с22п Ду 100 Ру 16 — 8 шт
+1.3/109 — Кран шаровой 11С67П Ду 100 Ру 16 — 2 шт
+1.3/110 — Кран шаровой 11С67П Ду 150 Ру 16 — 2 шт
+1.3/111 — Кран шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.3/112 — Кран шаровой 11С67П Ду 80 Ру 16 — 2 шт
+1.3/113 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 62 шт
+1.3/114 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 48 шт
+1.3/115 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 40 шт
+1.3/116 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 38 шт
+1.3/117 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 44 шт
+1.3/118 — Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку — 26 шт
+1.3/119 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 24 шт
+1.3/120 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 22 шт
+1.3/121 — Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку — 10 шт
+1.3/122 — Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 3 шт
+1.3/123 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/124 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.3/125 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/126 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.3/127 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 91 шт
+1.3/128 — Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 10 шт
+1.3/129 — Кран шаровой 11с67п Ду 150 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 59 шт
+1.3/130 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 45 шт
+1.3/131 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 8 шт
+1.3/132 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 80 шт
+1.3/133 — Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.3/134 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 92 шт
+1.3/136 — Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ — 14 шт
+1.3/137 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 29 шт
+1.3/138 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ — 6 шт
+1.3/139 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 31 шт
+1.3/140 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 8 шт
+1.3/141 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ — 8 шт
+1.3/142 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 8 шт
+1.3/143 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 112 шт
+1.3/144 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ — 6 шт
+1.3/145 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ — 58 шт
+1.3/146 — Кран шаровый химический КШХ Ду 50 Ру 16 — 2 шт
+1.3/147 — Кран шаровый химический КШХ Ду 80 Ру 16 — 4 шт
+1.3/148 — Кран шаровый разборный полнопроходной 11с67п Ду 250 Ру 16 с КОФ — 6 шт
+1.3/149 — Кран шаровый цельносварной неполнопроходной 11с67п Ду 250/200 Ру 16 с КОФ — 2 шт
+1.5/9 — Кран шаровой 11с22п Ду 50 Ру 16 — 4 шт
+1.5/10 — Кран шаровой 11с22п Ду 80 Ру 16 — 4 шт
+1.5/11 — Кран шаровой 11с22п Ду 100 Ру 16 — 2 шт
+1.5/12 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 25 шт
+1.5/13 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 32 шт
+1.5/14 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 15 шт
+1.5/15 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 26 шт
+1.5/16 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 9 шт
+1.5/17 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.5/18 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.6/57 — Кран шаровой 11с22п Ду 32 Ру 16 — 55 шт
+1.6/58 — Кран шаровой 11с22п Ду 50 Ру 16 — 35 шт
+1.6/59 — Кран шаровой 11с22п Ду 80 Ру 16 — 24 шт
+1.6/60 — Кран шаровой 11с22п Ду 100 Ру 16 — 27 шт
+1.6/61 — Кран шаровой 11с22п Ду 150 Ру 16 — 13 шт
+1.6/62 — Кран шаровой 11с22п Ду 200 Ру 16 — 3 шт
+1.6/63 — Кран запорный шаровой 11С67П Ду 100 Ру 16 — 25 шт
+1.6/64 — Кран запорный шаровой 11С67П Ду 150 Ру 16 — 9 шт
+1.6/65 — Кран запорный шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.6/66 — Кран запорный шаровой 11С67П Ду 50 Ру 16 — 25 шт
+1.6/67 — Кран запорный шаровой 11С67П Ду 80 Ру 16 — 22 шт
+1.6/68 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 36 шт
+1.6/69 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 6 шт
+1.6/70 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.6/71 — Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/72 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/73 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.6/74 — Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/75 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/76 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/77 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 4 шт
+1.6/78 — Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/79 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/80 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 3 шт
+1.6/81 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.6/82 — Кран шаровой TEMPER 28020025 муфтовый, Ду 25, Ру 40 — 2 шт
+1.6/83 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 3 шт
+1.6/84 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 1 шт
+1.6/85 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 2 шт
+1.6/86 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 6 шт
+1.6/87 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 5 шт
+1.6/88 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ — 6 шт
+1.7/2 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 12 шт
+1.7/3 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 12 шт
+1.7/4 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.8/2 — Кран шаровой 10нж45фт 2ЦФ Ду 20 Ру 16 — 2 шт
+1.8/3 — Кран шаровой 10нж45фт 2ЦФ Ду 25 Ру 16 — 2 шт
+1.8/4 — Кран шаровой 10нж45фт 2ЦФ Ду 32 Ру 16 — 2 шт
+1.8/5 — Кран шаровой 11с22п Ду 80 Ру 16 — 2 шт
+1.8/6 — Кран шаровой 11с22п Ду 100 Ру 16 — 1 шт
+1.8/7 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="409" customHeight="1">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Уральский завод трубопроводной арматуры» (УЗТА)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>uzta@mail.ru</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 99 поз.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/20 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.1/21 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.2/1 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 2 шт
+1.2/2 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.2/3 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 18 шт
+1.2/4 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.2/5 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.3/106 — Кран шаровой фланцевый 11с22п Ду 50 Ру 16 — 7 шт
+1.3/107 — Кран шаровой фланцевый 11с22п Ду 80 Ру 16 — 8 шт
+1.3/108 — Кран шаровой фланцевый 11с22п Ду 100 Ру 16 — 8 шт
+1.3/109 — Кран шаровой 11С67П Ду 100 Ру 16 — 2 шт
+1.3/110 — Кран шаровой 11С67П Ду 150 Ру 16 — 2 шт
+1.3/111 — Кран шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.3/112 — Кран шаровой 11С67П Ду 80 Ру 16 — 2 шт
+1.3/113 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 62 шт
+1.3/114 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 48 шт
+1.3/115 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 40 шт
+1.3/116 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 38 шт
+1.3/117 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 44 шт
+1.3/118 — Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку — 26 шт
+1.3/119 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 24 шт
+1.3/120 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 22 шт
+1.3/121 — Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку — 10 шт
+1.3/122 — Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 3 шт
+1.3/123 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/124 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.3/125 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/126 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.3/127 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 91 шт
+1.3/128 — Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 10 шт
+1.3/129 — Кран шаровой 11с67п Ду 150 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 59 шт
+1.3/130 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 45 шт
+1.3/131 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 8 шт
+1.3/132 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 80 шт
+1.3/133 — Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.3/134 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 92 шт
+1.3/136 — Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ — 14 шт
+1.3/137 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 29 шт
+1.3/138 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ — 6 шт
+1.3/139 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 31 шт
+1.3/140 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 8 шт
+1.3/141 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ — 8 шт
+1.3/142 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 8 шт
+1.3/143 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 112 шт
+1.3/144 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ — 6 шт
+1.3/145 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ — 58 шт
+1.3/148 — Кран шаровый разборный полнопроходной 11с67п Ду 250 Ру 16 с КОФ — 6 шт
+1.3/149 — Кран шаровый цельносварной неполнопроходной 11с67п Ду 250/200 Ру 16 с КОФ — 2 шт
+1.5/9 — Кран шаровой 11с22п Ду 50 Ру 16 — 4 шт
+1.5/10 — Кран шаровой 11с22п Ду 80 Ру 16 — 4 шт
+1.5/11 — Кран шаровой 11с22п Ду 100 Ру 16 — 2 шт
+1.5/12 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 25 шт
+1.5/13 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 32 шт
+1.5/14 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 15 шт
+1.5/15 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 26 шт
+1.5/16 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 9 шт
+1.5/17 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.5/18 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.6/57 — Кран шаровой 11с22п Ду 32 Ру 16 — 55 шт
+1.6/58 — Кран шаровой 11с22п Ду 50 Ру 16 — 35 шт
+1.6/59 — Кран шаровой 11с22п Ду 80 Ру 16 — 24 шт
+1.6/60 — Кран шаровой 11с22п Ду 100 Ру 16 — 27 шт
+1.6/61 — Кран шаровой 11с22п Ду 150 Ру 16 — 13 шт
+1.6/62 — Кран шаровой 11с22п Ду 200 Ру 16 — 3 шт
+1.6/63 — Кран запорный шаровой 11С67П Ду 100 Ру 16 — 25 шт
+1.6/64 — Кран запорный шаровой 11С67П Ду 150 Ру 16 — 9 шт
+1.6/65 — Кран запорный шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.6/66 — Кран запорный шаровой 11С67П Ду 50 Ру 16 — 25 шт
+1.6/67 — Кран запорный шаровой 11С67П Ду 80 Ру 16 — 22 шт
+1.6/68 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 36 шт
+1.6/69 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 6 шт
+1.6/70 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.6/71 — Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/72 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/73 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.6/74 — Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/75 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/76 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/77 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 4 шт
+1.6/78 — Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/79 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/80 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 3 шт
+1.6/81 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.6/82 — Кран шаровой TEMPER 28020025 муфтовый, Ду 25, Ру 40 — 2 шт
+1.6/83 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 3 шт
+1.6/84 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 1 шт
+1.6/85 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 2 шт
+1.6/86 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 6 шт
+1.6/87 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 5 шт
+1.6/88 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ — 6 шт
+1.7/2 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 12 шт
+1.7/3 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 12 шт
+1.7/4 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.8/2 — Кран шаровой 10нж45фт 2ЦФ Ду 20 Ру 16 — 2 шт
+1.8/3 — Кран шаровой 10нж45фт 2ЦФ Ду 25 Ру 16 — 2 шт
+1.8/4 — Кран шаровой 10нж45фт 2ЦФ Ду 32 Ру 16 — 2 шт
+1.8/5 — Кран шаровой 11с22п Ду 80 Ру 16 — 2 шт
+1.8/6 — Кран шаровой 11с22п Ду 100 Ру 16 — 1 шт
+1.8/7 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="409" customHeight="1">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>ООО «АЛСО» (завод стальных шаровых кранов ALSO)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>info@alsoarm.ru</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 96 поз.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/20 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.1/21 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.2/1 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 2 шт
+1.2/2 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.2/3 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 18 шт
+1.2/4 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.2/5 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.3/106 — Кран шаровой фланцевый 11с22п Ду 50 Ру 16 — 7 шт
+1.3/107 — Кран шаровой фланцевый 11с22п Ду 80 Ру 16 — 8 шт
+1.3/108 — Кран шаровой фланцевый 11с22п Ду 100 Ру 16 — 8 шт
+1.3/109 — Кран шаровой 11С67П Ду 100 Ру 16 — 2 шт
+1.3/110 — Кран шаровой 11С67П Ду 150 Ру 16 — 2 шт
+1.3/111 — Кран шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.3/112 — Кран шаровой 11С67П Ду 80 Ру 16 — 2 шт
+1.3/113 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 62 шт
+1.3/114 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 48 шт
+1.3/115 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 40 шт
+1.3/116 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 38 шт
+1.3/117 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 44 шт
+1.3/118 — Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку — 26 шт
+1.3/119 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 24 шт
+1.3/120 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 22 шт
+1.3/121 — Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку — 10 шт
+1.3/122 — Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 3 шт
+1.3/123 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/124 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.3/125 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/126 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.3/127 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 91 шт
+1.3/128 — Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 10 шт
+1.3/129 — Кран шаровой 11с67п Ду 150 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 59 шт
+1.3/130 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 45 шт
+1.3/131 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 8 шт
+1.3/132 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 80 шт
+1.3/133 — Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.3/134 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 92 шт
+1.3/136 — Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ — 14 шт
+1.3/137 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 29 шт
+1.3/138 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ — 6 шт
+1.3/139 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 31 шт
+1.3/140 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 8 шт
+1.3/141 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ — 8 шт
+1.3/142 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 8 шт
+1.3/143 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 112 шт
+1.3/144 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ — 6 шт
+1.3/145 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ — 58 шт
+1.3/148 — Кран шаровый разборный полнопроходной 11с67п Ду 250 Ру 16 с КОФ — 6 шт
+1.3/149 — Кран шаровый цельносварной неполнопроходной 11с67п Ду 250/200 Ру 16 с КОФ — 2 шт
+1.5/9 — Кран шаровой 11с22п Ду 50 Ру 16 — 4 шт
+1.5/10 — Кран шаровой 11с22п Ду 80 Ру 16 — 4 шт
+1.5/11 — Кран шаровой 11с22п Ду 100 Ру 16 — 2 шт
+1.5/12 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 25 шт
+1.5/13 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 32 шт
+1.5/14 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 15 шт
+1.5/15 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 26 шт
+1.5/16 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 9 шт
+1.5/17 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.5/18 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.6/57 — Кран шаровой 11с22п Ду 32 Ру 16 — 55 шт
+1.6/58 — Кран шаровой 11с22п Ду 50 Ру 16 — 35 шт
+1.6/59 — Кран шаровой 11с22п Ду 80 Ру 16 — 24 шт
+1.6/60 — Кран шаровой 11с22п Ду 100 Ру 16 — 27 шт
+1.6/61 — Кран шаровой 11с22п Ду 150 Ру 16 — 13 шт
+1.6/62 — Кран шаровой 11с22п Ду 200 Ру 16 — 3 шт
+1.6/63 — Кран запорный шаровой 11С67П Ду 100 Ру 16 — 25 шт
+1.6/64 — Кран запорный шаровой 11С67П Ду 150 Ру 16 — 9 шт
+1.6/65 — Кран запорный шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.6/66 — Кран запорный шаровой 11С67П Ду 50 Ру 16 — 25 шт
+1.6/67 — Кран запорный шаровой 11С67П Ду 80 Ру 16 — 22 шт
+1.6/68 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 36 шт
+1.6/69 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 6 шт
+1.6/70 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.6/71 — Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/72 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/73 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.6/74 — Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/75 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/76 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/77 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 4 шт
+1.6/78 — Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/79 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/80 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 3 шт
+1.6/81 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.6/82 — Кран шаровой TEMPER 28020025 муфтовый, Ду 25, Ру 40 — 2 шт
+1.6/83 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 3 шт
+1.6/84 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 1 шт
+1.6/85 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 2 шт
+1.6/86 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 6 шт
+1.6/87 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 5 шт
+1.6/88 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ — 6 шт
+1.7/2 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 12 шт
+1.7/3 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 12 шт
+1.7/4 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.8/5 — Кран шаровой 11с22п Ду 80 Ру 16 — 2 шт
+1.8/6 — Кран шаровой 11с22п Ду 100 Ру 16 — 1 шт
+1.8/7 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="409" customHeight="1">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>РОБЕН (ранее БРОЕН; ТМ «Балломакс») — завод в Коломне</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>info@robenvalves.ru</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 96 поз.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/20 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.1/21 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.2/1 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 2 шт
+1.2/2 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.2/3 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 18 шт
+1.2/4 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.2/5 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.3/106 — Кран шаровой фланцевый 11с22п Ду 50 Ру 16 — 7 шт
+1.3/107 — Кран шаровой фланцевый 11с22п Ду 80 Ру 16 — 8 шт
+1.3/108 — Кран шаровой фланцевый 11с22п Ду 100 Ру 16 — 8 шт
+1.3/109 — Кран шаровой 11С67П Ду 100 Ру 16 — 2 шт
+1.3/110 — Кран шаровой 11С67П Ду 150 Ру 16 — 2 шт
+1.3/111 — Кран шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.3/112 — Кран шаровой 11С67П Ду 80 Ру 16 — 2 шт
+1.3/113 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 62 шт
+1.3/114 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 48 шт
+1.3/115 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 40 шт
+1.3/116 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 38 шт
+1.3/117 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 44 шт
+1.3/118 — Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку — 26 шт
+1.3/119 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 24 шт
+1.3/120 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 22 шт
+1.3/121 — Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку — 10 шт
+1.3/122 — Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 3 шт
+1.3/123 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/124 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.3/125 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/126 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.3/127 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 91 шт
+1.3/128 — Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 10 шт
+1.3/129 — Кран шаровой 11с67п Ду 150 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 59 шт
+1.3/130 — Кран шаровой 11с67п Ду 200 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 45 шт
+1.3/131 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 8 шт
+1.3/132 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 80 шт
+1.3/133 — Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.3/134 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 92 шт
+1.3/136 — Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ — 14 шт
+1.3/137 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 29 шт
+1.3/138 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ — 6 шт
+1.3/139 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 31 шт
+1.3/140 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 8 шт
+1.3/141 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ — 8 шт
+1.3/142 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 8 шт
+1.3/143 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 112 шт
+1.3/144 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ — 6 шт
+1.3/145 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ — 58 шт
+1.3/148 — Кран шаровый разборный полнопроходной 11с67п Ду 250 Ру 16 с КОФ — 6 шт
+1.3/149 — Кран шаровый цельносварной неполнопроходной 11с67п Ду 250/200 Ру 16 с КОФ — 2 шт
+1.5/9 — Кран шаровой 11с22п Ду 50 Ру 16 — 4 шт
+1.5/10 — Кран шаровой 11с22п Ду 80 Ру 16 — 4 шт
+1.5/11 — Кран шаровой 11с22п Ду 100 Ру 16 — 2 шт
+1.5/12 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 25 шт
+1.5/13 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 32 шт
+1.5/14 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 15 шт
+1.5/15 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 26 шт
+1.5/16 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 9 шт
+1.5/17 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.5/18 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.6/57 — Кран шаровой 11с22п Ду 32 Ру 16 — 55 шт
+1.6/58 — Кран шаровой 11с22п Ду 50 Ру 16 — 35 шт
+1.6/59 — Кран шаровой 11с22п Ду 80 Ру 16 — 24 шт
+1.6/60 — Кран шаровой 11с22п Ду 100 Ру 16 — 27 шт
+1.6/61 — Кран шаровой 11с22п Ду 150 Ру 16 — 13 шт
+1.6/62 — Кран шаровой 11с22п Ду 200 Ру 16 — 3 шт
+1.6/63 — Кран запорный шаровой 11С67П Ду 100 Ру 16 — 25 шт
+1.6/64 — Кран запорный шаровой 11С67П Ду 150 Ру 16 — 9 шт
+1.6/65 — Кран запорный шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.6/66 — Кран запорный шаровой 11С67П Ду 50 Ру 16 — 25 шт
+1.6/67 — Кран запорный шаровой 11С67П Ду 80 Ру 16 — 22 шт
+1.6/68 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 36 шт
+1.6/69 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 6 шт
+1.6/70 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.6/71 — Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/72 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/73 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.6/74 — Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/75 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/76 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/77 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 4 шт
+1.6/78 — Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/79 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/80 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 3 шт
+1.6/81 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.6/82 — Кран шаровой TEMPER 28020025 муфтовый, Ду 25, Ру 40 — 2 шт
+1.6/83 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 3 шт
+1.6/84 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 150 Ру 16 с КОФ — 1 шт
+1.6/85 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 2 шт
+1.6/86 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 6 шт
+1.6/87 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 5 шт
+1.6/88 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ — 6 шт
+1.7/2 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 12 шт
+1.7/3 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 12 шт
+1.7/4 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.8/5 — Кран шаровой 11с22п Ду 80 Ру 16 — 2 шт
+1.8/6 — Кран шаровой 11с22п Ду 100 Ру 16 — 1 шт
+1.8/7 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Краны Балашихи» (КБ)</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>sales@kb-arm.ru</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 89 поз.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/20 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.2/1 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 2 шт
+1.2/2 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.2/3 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 18 шт
+1.2/4 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.2/5 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 2 шт
+1.3/106 — Кран шаровой фланцевый 11с22п Ду 50 Ру 16 — 7 шт
+1.3/107 — Кран шаровой фланцевый 11с22п Ду 80 Ру 16 — 8 шт
+1.3/108 — Кран шаровой фланцевый 11с22п Ду 100 Ру 16 — 8 шт
+1.3/109 — Кран шаровой 11С67П Ду 100 Ру 16 — 2 шт
+1.3/110 — Кран шаровой 11С67П Ду 150 Ру 16 — 2 шт
+1.3/111 — Кран шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.3/112 — Кран шаровой 11С67П Ду 80 Ру 16 — 2 шт
+1.3/113 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 62 шт
+1.3/114 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 48 шт
+1.3/115 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 40 шт
+1.3/116 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 38 шт
+1.3/117 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 44 шт
+1.3/118 — Кран шаровой 11с67п Ду 80 Ру 25 цельносварной под приварку — 26 шт
+1.3/119 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 24 шт
+1.3/120 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 22 шт
+1.3/121 — Кран шаровой 11с67п Ду 200 Ру 25 цельносварной под приварку — 10 шт
+1.3/122 — Кран шаровой 11с67п Ду 15 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 3 шт
+1.3/123 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/124 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.3/125 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 6 шт
+1.3/126 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+1.3/127 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 91 шт
+1.3/128 — Кран шаровой 11с67п Ду 125 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 10 шт
+1.3/131 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 8 шт
+1.3/132 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 80 шт
+1.3/133 — Кран шаровой 11с67п Ду 65 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.3/134 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 92 шт
+1.3/136 — Кран шаровый LD неполнопроходной 11с67п КШЦФ Ду 200 Ру 16 с КОФ — 14 шт
+1.3/137 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 29 шт
+1.3/138 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 125 Ру 16 с КОФ — 6 шт
+1.3/140 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 8 шт
+1.3/141 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 32 Ру 16 с КОФ — 8 шт
+1.3/142 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 8 шт
+1.3/143 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 112 шт
+1.3/144 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 65 Ру 16 с КОФ — 6 шт
+1.3/145 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 МПа с КОФ — 58 шт
+1.5/9 — Кран шаровой 11с22п Ду 50 Ру 16 — 4 шт
+1.5/10 — Кран шаровой 11с22п Ду 80 Ру 16 — 4 шт
+1.5/11 — Кран шаровой 11с22п Ду 100 Ру 16 — 2 шт
+1.5/12 — Кран шаровой 11с67п Ду 15 Ру 25 цельносварной под приварку — 25 шт
+1.5/13 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 32 шт
+1.5/14 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 15 шт
+1.5/15 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 26 шт
+1.5/16 — Кран шаровой 11с67п Ду 50 Ру 25 цельносварной под приварку — 9 шт
+1.5/17 — Кран шаровой 11с67п Ду 100 Ру 25 цельносварной под приварку — 4 шт
+1.5/18 — Кран шаровой 11с67п Ду 150 Ру 25 цельносварной под приварку — 2 шт
+1.6/57 — Кран шаровой 11с22п Ду 32 Ру 16 — 55 шт
+1.6/58 — Кран шаровой 11с22п Ду 50 Ру 16 — 35 шт
+1.6/59 — Кран шаровой 11с22п Ду 80 Ру 16 — 24 шт
+1.6/60 — Кран шаровой 11с22п Ду 100 Ру 16 — 27 шт
+1.6/61 — Кран шаровой 11с22п Ду 150 Ру 16 — 13 шт
+1.6/62 — Кран шаровой 11с22п Ду 200 Ру 16 — 3 шт
+1.6/63 — Кран запорный шаровой 11С67П Ду 100 Ру 16 — 25 шт
+1.6/64 — Кран запорный шаровой 11С67П Ду 150 Ру 16 — 9 шт
+1.6/65 — Кран запорный шаровой 11С67П Ду 200 Ру 16 — 2 шт
+1.6/66 — Кран запорный шаровой 11С67П Ду 50 Ру 16 — 25 шт
+1.6/67 — Кран запорный шаровой 11С67П Ду 80 Ру 16 — 22 шт
+1.6/68 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 36 шт
+1.6/69 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 6 шт
+1.6/70 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.6/71 — Кран шаровой 11с67п Ду 20 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/72 — Кран шаровой 11с67п Ду 25 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/73 — Кран шаровой 11с67п Ду 32 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 10 шт
+1.6/74 — Кран шаровой 11с67п Ду 40 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 2 шт
+1.6/75 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/76 — Кран шаровой 11с67п Ду 80 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 9 шт
+1.6/77 — Кран шаровой 11с67п Ду 100 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 4 шт
+1.6/78 — Кран шаровой 11с67п Ду 32 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/79 — Кран шаровой 11с67п Ду 40 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 1 шт
+1.6/80 — Кран шаровой 11с67п Ду 50 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 3 шт
+1.6/81 — Кран шаровой 11с67п Ду 80 Ру 16 ЦУФ.001 КШ укороченный полнопроходной фланцевый с рукояткой — 6 шт
+1.6/82 — Кран шаровой TEMPER 28020025 муфтовый, Ду 25, Ру 40 — 2 шт
+1.6/83 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 100 Ру 16 с КОФ — 3 шт
+1.6/85 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 25 Ру 16 с КОФ — 2 шт
+1.6/86 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 40 Ру 16 с КОФ — 6 шт
+1.6/87 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 50 Ру 16 с КОФ — 5 шт
+1.6/88 — Кран шаровый LD полнопроходной 11с67п КШРФ Ду 80 Ру 16 с КОФ — 6 шт
+1.7/2 — Кран шаровой 11с67п Ду 25 Ру 25 цельносварной под приварку — 12 шт
+1.7/3 — Кран шаровой 11с67п Ду 32 Ру 25 цельносварной под приварку — 12 шт
+1.7/4 — Кран шаровой 11с67п Ду 40 Ру 25 цельносварной под приварку — 10 шт
+1.8/5 — Кран шаровой 11с22п Ду 80 Ру 16 — 2 шт
+1.8/6 — Кран шаровой 11с22п Ду 100 Ру 16 — 1 шт
+1.8/7 — Кран шаровой 11с67п Ду 50 Ру 25 полнопрох. с КОФ (КЗШС41нж) — 4 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="390" customHeight="1">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ГАЛЛОП» (Новосибирский арматурный завод)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>info@gallop.ru</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 22 поз.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/14 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 35 шт
+1.1/15 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 35 шт
+1.1/16 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 20 шт
+1.1/17 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 25 шт
+1.1/18 — Кран шаровой 11б27п1 Ду 40 Ру 16 — 8 шт
+1.1/19 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 8 шт
+1.3/101 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 110 шт
+1.3/102 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 57 шт
+1.3/103 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 29 шт
+1.3/104 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 47 шт
+1.3/105 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 24 шт
+1.5/4 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 28 шт
+1.5/5 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 16 шт
+1.5/6 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 16 шт
+1.5/7 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 6 шт
+1.5/8 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 6 шт
+1.6/51 — Кран шаровой 11б27п1 Ду 15 Ру 16 — 47 шт
+1.6/52 — Кран шаровой 11б27п1 Ду 20 Ру 16 — 63 шт
+1.6/53 — Кран шаровой 11б27п1 Ду 25 Ру 16 — 40 шт
+1.6/54 — Кран шаровой 11б27п1 Ду 32 Ру 16 — 77 шт
+1.6/55 — Кран шаровой 11б27п1 Ду 40 Ру 16 — 2 шт
+1.6/56 — Кран шаровой 11б27п1 Ду 50 Ру 16 — 6 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="150" customHeight="1">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Компания «Арматон»</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>armaton@bk.ru</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 6 поз.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/40 — Клапан 22б16п (15б34бк1) запорный вакуумный сильфонный Ду6 Ру16 — 2 шт
+1.3/45 — Клапан запорный 14нж17п Ду 15 Ру 10 цапковый — 2 шт
+1.3/46 — Клапан запорный 14нж17п Ду 25 Ру 10 цапковый — 2 шт
+1.3/47 — Клапан запорный 14нж17п Ду 32 Ру 10 цапковый — 1 шт
+1.3/56 — Клапан запорны 15нж65нж Ду 125 Ру 16 фланцевый — 1 шт
+1.3/57 — Клапан запорны 15нж65нж Ду 150 Ру 16 фланцевый — 3 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="135" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Арма-Пром» (Старооскольский арматурный завод, ГК «Авангард», ТМ САЗ)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>zavod@saz-avangard.ru</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 5 поз.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/2 — Клапан регулирующий 25ч945п Ду 15 Ру 16 с ЭИМ — 2 шт
+1.3/3 — Клапан регулирующий 25ч945п Ду 25 Ру 16 с ЭИМ — 1 шт
+1.3/4 — Клапан регулирующий 25ч945п Ду 50 Ру 16 KV100 с ЭИМ — 2 шт
+1.3/5 — Клапан регулирующий 25ч945п Ду 80 Ру 16 с ЭИМ — 8 шт
+1.3/163 — Электропривод прямоходный Regada SТ0 490.0-00TQV/00 — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Пермский трубопроводный завод» (ООО «ПТЗ»)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>sales@ptza.ru</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 4 поз.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/23 — Клапан обратный 16нж10нж Ду 50 Ру 16 — 2 шт
+1.3/24 — Клапан обратный 16нж10нж Ду 32 Ру16 — 5 шт
+1.3/56 — Клапан запорны 15нж65нж Ду 125 Ру 16 фланцевый — 1 шт
+1.3/57 — Клапан запорны 15нж65нж Ду 150 Ру 16 фланцевый — 3 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="105" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ПромАрм» (PromArm®)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>info@promarm.ru</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 3 поз.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/22 — Затвор дисковый поворотный межфланцевый Stensel 31070-01 Ду 200 Ру 25 — 3 шт
+1.1/23 — Затвор дисковый поворотный межфланцевый ПА954.450.10-05 Ду 450 Ру 10 — 1 шт
+1.3/150 — Затвор 32нж910р Ду 1000 Ру 10 с эл.приводом — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="105" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>АО «Пензтяжпромарматура» (АО «ПТПА»)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>sales@ptpa.ru</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 3 поз.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/22 — Затвор дисковый поворотный межфланцевый Stensel 31070-01 Ду 200 Ру 25 — 3 шт
+1.1/23 — Затвор дисковый поворотный межфланцевый ПА954.450.10-05 Ду 450 Ру 10 — 1 шт
+1.3/150 — Затвор 32нж910р Ду 1000 Ру 10 с эл.приводом — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="105" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Челябинский завод трубопроводной арматуры» (ООО «ЧЗТА», бренд «ЧЗТА АРМАКОМ»)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>zakaz@chzta.ru</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 3 поз.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/6 — Задвижка 30нж947нж Ду 1000 Ру 4 — 1 шт
+1.3/23 — Клапан обратный 16нж10нж Ду 50 Ру 16 — 2 шт
+1.3/24 — Клапан обратный 16нж10нж Ду 32 Ру16 — 5 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="105" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Нижегородский завод «Старт»</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>start.nn@mail.ru</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 3 поз.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/45 — Клапан запорный 14нж17п Ду 15 Ру 10 цапковый — 2 шт
+1.3/46 — Клапан запорный 14нж17п Ду 25 Ру 10 цапковый — 2 шт
+1.3/47 — Клапан запорный 14нж17п Ду 32 Ру 10 цапковый — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="105" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>АО «Пензенский арматурный завод» (АО «ПАЗ»)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>info@armpaz.ru</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 3 поз.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/22 — Затвор дисковый поворотный межфланцевый Stensel 31070-01 Ду 200 Ру 25 — 3 шт
+1.1/23 — Затвор дисковый поворотный межфланцевый ПА954.450.10-05 Ду 450 Ру 10 — 1 шт
+1.3/150 — Затвор 32нж910р Ду 1000 Ру 10 с эл.приводом — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>АО «УралТехКомплектация» (ТМ «MV»)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>info@aoutk.ru</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 2 поз.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/22 — Затвор дисковый поворотный межфланцевый Stensel 31070-01 Ду 200 Ру 25 — 3 шт
+1.1/23 — Затвор дисковый поворотный межфланцевый ПА954.450.10-05 Ду 450 Ру 10 — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>АО «АБС ЗЭиМ Автоматизация»</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>sales@zeim.ru</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 2 поз.</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/163 — Электропривод прямоходный Regada SТ0 490.0-00TQV/00 — 1 шт
+1.6/93 — Электропривод Esbe 95 - 12051900 — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ООО ПО «Нефтехимавтоматика» (НХА)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>zakaz@nhavtomatika.ru</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 2 поз.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.1/22 — Затвор дисковый поворотный межфланцевый Stensel 31070-01 Ду 200 Ру 25 — 3 шт
+1.1/23 — Затвор дисковый поворотный межфланцевый ПА954.450.10-05 Ду 450 Ру 10 — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="75" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ЗАО «Арматурная Компания «ФОБОС»</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>info@fobosarm.ru</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/135 — Кран шаровой нержавеющий G1/2" муфтовый, полнопроходной, Ду 15 Ру 63 — 19 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="75" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>ООО «НПП «Промышленная автоматика» (НПП «ПРОМА»)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>info@promav.ru</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/163 — Электропривод прямоходный Regada SТ0 490.0-00TQV/00 — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="75" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ПКФ «ТЕРМ»</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>term1998@yandex.ru</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.4/1 — Рыбозащитное устройство с потокообразователем — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="75" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Регул»</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>regyl21@mail.ru</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.4/1 — Рыбозащитное устройство с потокообразователем — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="75" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ПЭК — «Поволжская Электротехническая Компания» (сайт piek.ru)</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>info@piek.ru</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/163 — Электропривод прямоходный Regada SТ0 490.0-00TQV/00 — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="75" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>ТЕД Газовые системы (TEDGAS; сервисный центр DUNGS; домен dungs.ru ведёт на tedgas.ru)</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>info@tedgas.ru (отдел продаж: retail@karldungs.ru)</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.6/92 — Газовый клапан Dungs LGV 507/5 230 V, 119271 — 2 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="75" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Фирменный магазин ESBE (esbeshop.ru)</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>info@esbeshop.ru</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.6/93 — Электропривод Esbe 95 - 12051900 — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="75" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>ООО «Аврора» (avrora-arm.ru)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>sales@avrora-arm.ru</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/163 — Электропривод прямоходный Regada SТ0 490.0-00TQV/00 — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="75" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>ООО «ПО БЗТпА» (Брянский завод трубопроводной арматуры, bztpa.ru)</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>info@bztpa.ru</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Запрос КП: арматура для Камчатскэнерго, 1 поз.</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Добрый день!
+ООО «ГИДРОПАС» (ИНН 9729231965) готовит заявку на поставку трубопроводной арматуры для АО «Камчатскэнерго» (закупка 32616346943). Просим коммерческое предложение на позиции ниже — строго по техническим требованиям (полные характеристики — во вложении):
+1.3/150 — Затвор 32нж910р Ду 1000 Ру 10 с эл.приводом — 1 шт
+В КП просим указать: цену за единицу с НДС, срок изготовления/отгрузки, условия оплаты, страну производства и номер реестровой записи Минпромторга (ПП 719), наличие сертификатов/деклараций ТР ТС 010/2011 и 032/2013, вес и габариты для доставки до Петропавловска-Камчатского. Если какая-то позиция выпускается в другом исполнении — укажите отличия от ТЗ.
+Ответ нужен до 30.10.2026.
+С уважением,
+ООО «ГИДРОПАС»</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3332,7 +5156,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16504,7 +18328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17267,7 +19091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18795,7 +20619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19051,7 +20875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
